--- a/要件定義書.xlsx
+++ b/要件定義書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\渡辺のぞみ\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE9CBDA-68FC-4291-84CB-022C5C5913B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA89139-32F6-4FE9-8B10-E2DBE31EE522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="142">
   <si>
     <t>要件定義</t>
   </si>
@@ -137,43 +137,16 @@
     <t>1-1. システム化の背景</t>
   </si>
   <si>
-    <t>当社の営業部門では、見積作成業務が担当者ごとに個別管理されており、最新版の不一致、承認漏れ、作業遅延といった問題が発生している。</t>
-  </si>
-  <si>
-    <t>これらの課題を解消するため、標準化された見積管理システムの構築が必要となった。</t>
-  </si>
-  <si>
     <t>1-2. システム化の目的</t>
   </si>
   <si>
-    <t>本システムの導入により、見積作成の標準化と承認フローの一元管理を実現し、作業時間の削減と情報共有の精度向上を図る。</t>
-  </si>
-  <si>
     <t>1-3. システム化の範囲</t>
   </si>
   <si>
     <t>[対象範囲]</t>
   </si>
   <si>
-    <t>営業部による見積作成業務</t>
-  </si>
-  <si>
-    <t>承認フローの整備</t>
-  </si>
-  <si>
-    <t>顧客・商品マスタの参照</t>
-  </si>
-  <si>
-    <t>既存システムとの簡易連携（CSV取り込みのみ）</t>
-  </si>
-  <si>
     <t>[対象外]</t>
-  </si>
-  <si>
-    <t>複雑な在庫管理機能</t>
-  </si>
-  <si>
-    <t>価格自動決定アルゴリズム</t>
   </si>
   <si>
     <t>1-4. 現状（As-Is）</t>
@@ -646,6 +619,173 @@
   </si>
   <si>
     <t>渡辺 のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接希望者数の増加に伴い、アクション必要数が増加し面接日時決定までの時間の遅れや、対応する人数を増員させることで発生する引継ぎ時間の効率化が必要であったため。</t>
+    <rPh sb="0" eb="6">
+      <t>メンセツキボウシャスウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ヒツヨウスウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="25" eb="31">
+      <t>メンセツニチジケッテイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ニンズウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ゾウイン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ヒキツ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>コウリツカ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>これらの課題を解消するため、見える化された採用管理システムの構築が必要となった。</t>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>本システムの導入により、採用数の増加に向けたアクションの見える化を実現し、情報共有時間の効率化・面接日程設定までの時間短縮による面接設定件数の増加・採用数の増加を図る。</t>
+    <rPh sb="37" eb="43">
+      <t>ジョウホウキョウユウジカン</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>コウリツカ</t>
+    </rPh>
+    <rPh sb="48" eb="52">
+      <t>メンセツニッテイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="66" eb="70">
+      <t>セッテイケンスウ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>サイヨウスウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接希望者一覧</t>
+    <rPh sb="0" eb="5">
+      <t>メンセツキボウシャ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接日時設定による対応結果（日時・担当者）の閲覧</t>
+    <rPh sb="0" eb="4">
+      <t>メンセツニチジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュール（カレンダー）への反映</t>
+    <rPh sb="15" eb="17">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接決定時、担当者へのメール配信</t>
+    <rPh sb="0" eb="5">
+      <t>メンセツケッテイジ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハイシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
     <rPh sb="0" eb="2">
       <t>ワタナベ</t>
     </rPh>
@@ -1321,6 +1461,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1333,17 +1491,77 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1363,75 +1581,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1462,41 +1611,32 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1906,44 +2046,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="74"/>
-      <c r="B6" s="75"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="72"/>
       <c r="C6" s="73"/>
-      <c r="D6" s="76" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="75"/>
+      <c r="D6" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="72"/>
       <c r="O6" s="73"/>
-      <c r="P6" s="74"/>
+      <c r="P6" s="71"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="74"/>
-      <c r="B7" s="75"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="72"/>
       <c r="C7" s="73"/>
-      <c r="D7" s="76" t="s">
+      <c r="D7" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-      <c r="L7" s="76"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="75"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="72"/>
       <c r="O7" s="73"/>
-      <c r="P7" s="74"/>
+      <c r="P7" s="71"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A8" s="8"/>
@@ -2005,16 +2145,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="70"/>
-      <c r="H11" s="71" t="s">
-        <v>142</v>
-      </c>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2027,16 +2167,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="69" t="s">
+      <c r="F12" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="70"/>
-      <c r="H12" s="127">
+      <c r="G12" s="76"/>
+      <c r="H12" s="79">
         <v>46265</v>
       </c>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2049,14 +2189,14 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="69" t="s">
+      <c r="F13" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="70"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2069,14 +2209,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="69" t="s">
+      <c r="F14" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="70"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -2213,22 +2353,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2241,52 +2381,52 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="95" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="88"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="102"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="93"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="100"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="91"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="102"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="93"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2"/>
@@ -2312,427 +2452,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103" t="s">
+      <c r="C4" s="95"/>
+      <c r="D4" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103" t="s">
+      <c r="E4" s="95"/>
+      <c r="F4" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="105"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="103" t="s">
+      <c r="G4" s="96"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="105"/>
-      <c r="Q4" s="105"/>
-      <c r="R4" s="104"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="95"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87"/>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
-      <c r="P5" s="87"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="88"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="101"/>
+      <c r="N5" s="101"/>
+      <c r="O5" s="101"/>
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="102"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="77"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="82"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="107"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="108"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="82"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="108"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="82"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="107"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="108"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="82"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="107"/>
+      <c r="O9" s="107"/>
+      <c r="P9" s="107"/>
+      <c r="Q9" s="107"/>
+      <c r="R9" s="108"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="77"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="82"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="107"/>
+      <c r="M10" s="107"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="107"/>
+      <c r="P10" s="107"/>
+      <c r="Q10" s="107"/>
+      <c r="R10" s="108"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="82"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="107"/>
+      <c r="L11" s="107"/>
+      <c r="M11" s="107"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="107"/>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="108"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="82"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="107"/>
+      <c r="K12" s="107"/>
+      <c r="L12" s="107"/>
+      <c r="M12" s="107"/>
+      <c r="N12" s="107"/>
+      <c r="O12" s="107"/>
+      <c r="P12" s="107"/>
+      <c r="Q12" s="107"/>
+      <c r="R12" s="108"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="82"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="107"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="107"/>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="107"/>
+      <c r="R13" s="108"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="82"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="107"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="107"/>
+      <c r="P14" s="107"/>
+      <c r="Q14" s="107"/>
+      <c r="R14" s="108"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="82"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="107"/>
+      <c r="P15" s="107"/>
+      <c r="Q15" s="107"/>
+      <c r="R15" s="108"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="82"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="104"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="107"/>
+      <c r="M16" s="107"/>
+      <c r="N16" s="107"/>
+      <c r="O16" s="107"/>
+      <c r="P16" s="107"/>
+      <c r="Q16" s="107"/>
+      <c r="R16" s="108"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="82"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="107"/>
+      <c r="M17" s="107"/>
+      <c r="N17" s="107"/>
+      <c r="O17" s="107"/>
+      <c r="P17" s="107"/>
+      <c r="Q17" s="107"/>
+      <c r="R17" s="108"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="77"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="82"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="107"/>
+      <c r="M18" s="107"/>
+      <c r="N18" s="107"/>
+      <c r="O18" s="107"/>
+      <c r="P18" s="107"/>
+      <c r="Q18" s="107"/>
+      <c r="R18" s="108"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="81"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="82"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="107"/>
+      <c r="M19" s="107"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="107"/>
+      <c r="P19" s="107"/>
+      <c r="Q19" s="107"/>
+      <c r="R19" s="108"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="77"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="81"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="82"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="107"/>
+      <c r="Q20" s="107"/>
+      <c r="R20" s="108"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="82"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="107"/>
+      <c r="O21" s="107"/>
+      <c r="P21" s="107"/>
+      <c r="Q21" s="107"/>
+      <c r="R21" s="108"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="82"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="107"/>
+      <c r="M22" s="107"/>
+      <c r="N22" s="107"/>
+      <c r="O22" s="107"/>
+      <c r="P22" s="107"/>
+      <c r="Q22" s="107"/>
+      <c r="R22" s="108"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5"/>
@@ -2876,6 +3016,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:R22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:O2"/>
     <mergeCell ref="Q1:R1"/>
@@ -2884,78 +3096,6 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:R4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:R22"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2968,23 +3108,23 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -2995,19 +3135,19 @@
       <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3040,14 +3180,14 @@
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="108"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="111"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3055,14 +3195,14 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="106" t="s">
+      <c r="K4" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="107"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="108"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="111"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3595,50 +3735,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A53200-138B-4730-BC3C-8EB91F016A0A}">
   <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="110" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112" t="s">
+      <c r="D1" s="114"/>
+      <c r="E1" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="114"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="117"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="40">
-        <v>46001</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -3686,44 +3829,44 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
-      <c r="B5" s="115" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="115"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="115"/>
+      <c r="B5" s="118" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="36"/>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="115"/>
-      <c r="N6" s="115"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
       <c r="O6" s="36"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -3759,7 +3902,7 @@
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -3778,7 +3921,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3814,7 +3957,7 @@
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="36"/>
       <c r="B12" s="36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -3832,115 +3975,113 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="36"/>
-      <c r="B13" s="109" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="109"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="109"/>
-      <c r="O13" s="109"/>
+      <c r="B13" s="112" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="112"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="36"/>
-      <c r="B14" s="109" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="109"/>
-      <c r="J14" s="109"/>
-      <c r="K14" s="109"/>
-      <c r="L14" s="109"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="109"/>
-      <c r="O14" s="109"/>
+      <c r="B14" s="112" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="36"/>
-      <c r="B15" s="109" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="109"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="109"/>
-      <c r="O15" s="109"/>
+      <c r="B15" s="112" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="36"/>
-      <c r="B16" s="109" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="109"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="109"/>
-      <c r="M16" s="109"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="109"/>
+      <c r="B16" s="112" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="36"/>
-      <c r="B17" s="109" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="109"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="109"/>
-      <c r="K17" s="109"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="109"/>
-      <c r="O17" s="109"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="I17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="36"/>
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109"/>
-      <c r="L18" s="109"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="109"/>
-      <c r="O18" s="109"/>
+      <c r="B18" s="112"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="36"/>
@@ -3962,7 +4103,7 @@
     <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="36"/>
       <c r="B20" s="43" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="44"/>
@@ -3981,7 +4122,7 @@
     <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -3999,9 +4140,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="36"/>
-      <c r="B22" s="43" t="s">
-        <v>46</v>
-      </c>
+      <c r="B22" s="43"/>
       <c r="C22" s="44"/>
       <c r="D22" s="44"/>
       <c r="E22" s="44"/>
@@ -4036,7 +4175,7 @@
     <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -4055,7 +4194,7 @@
     <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4074,7 +4213,7 @@
     <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4093,7 +4232,7 @@
     <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4112,7 +4251,7 @@
     <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="8"/>
       <c r="B28" s="46" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
@@ -4148,7 +4287,7 @@
     <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8"/>
       <c r="B30" s="8" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4167,7 +4306,7 @@
     <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4186,7 +4325,7 @@
     <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4205,7 +4344,7 @@
     <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8"/>
       <c r="B33" s="48" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -4224,7 +4363,7 @@
     <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="8"/>
       <c r="B34" s="48" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -4266,23 +4405,23 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="110" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="115" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="117"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -4297,17 +4436,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4337,7 +4476,7 @@
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4372,12 +4511,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="36"/>
-      <c r="B6" s="118" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="119"/>
+      <c r="B6" s="119" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="120"/>
       <c r="D6" s="50" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -4393,12 +4532,12 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
-      <c r="B7" s="116" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="117"/>
+      <c r="B7" s="121" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="122"/>
       <c r="D7" s="54" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -4414,12 +4553,12 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
-      <c r="B8" s="116" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="117"/>
+      <c r="B8" s="121" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="122"/>
       <c r="D8" s="54" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="55"/>
@@ -4436,11 +4575,11 @@
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C9" s="56"/>
       <c r="D9" s="54" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="55"/>
@@ -4456,12 +4595,12 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="36"/>
-      <c r="B10" s="116" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="117"/>
+      <c r="B10" s="121" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="122"/>
       <c r="D10" s="17" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
@@ -4902,15 +5041,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4923,23 +5062,23 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="110" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="115" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="117"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -4949,23 +5088,23 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="120">
+      <c r="O1" s="123">
         <v>46001</v>
       </c>
       <c r="P1" s="124"/>
     </row>
     <row r="2" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4997,7 +5136,7 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5034,18 +5173,18 @@
     </row>
     <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="36"/>
-      <c r="B6" s="118" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="119"/>
+      <c r="B6" s="119" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="120"/>
       <c r="D6" s="50" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
       <c r="G6" s="22"/>
       <c r="H6" s="50" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I6" s="51"/>
       <c r="J6" s="51"/>
@@ -5053,137 +5192,137 @@
       <c r="L6" s="52"/>
       <c r="M6" s="67"/>
       <c r="N6" s="50" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="O6" s="56"/>
       <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
-      <c r="B7" s="116" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="117"/>
+      <c r="B7" s="121" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="122"/>
       <c r="D7" s="54" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
       <c r="G7" s="56"/>
-      <c r="H7" s="122" t="s">
-        <v>113</v>
+      <c r="H7" s="69" t="s">
+        <v>104</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="55"/>
       <c r="K7" s="55"/>
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
-      <c r="N7" s="123" t="s">
-        <v>114</v>
+      <c r="N7" s="70" t="s">
+        <v>105</v>
       </c>
       <c r="O7" s="56"/>
       <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
-      <c r="B8" s="116" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="117"/>
+      <c r="B8" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="122"/>
       <c r="D8" s="54" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="55"/>
       <c r="G8" s="56"/>
-      <c r="H8" s="122" t="s">
-        <v>117</v>
+      <c r="H8" s="69" t="s">
+        <v>108</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="55"/>
       <c r="K8" s="55"/>
       <c r="L8" s="55"/>
       <c r="M8" s="56"/>
-      <c r="N8" s="123" t="s">
-        <v>118</v>
+      <c r="N8" s="70" t="s">
+        <v>109</v>
       </c>
       <c r="O8" s="56"/>
       <c r="P8" s="7"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
-      <c r="B9" s="116" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="117"/>
+      <c r="B9" s="121" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="122"/>
       <c r="D9" s="54" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="55"/>
       <c r="G9" s="56"/>
-      <c r="H9" s="122" t="s">
-        <v>121</v>
+      <c r="H9" s="69" t="s">
+        <v>112</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="55"/>
       <c r="K9" s="55"/>
       <c r="L9" s="55"/>
       <c r="M9" s="56"/>
-      <c r="N9" s="123" t="s">
-        <v>122</v>
+      <c r="N9" s="70" t="s">
+        <v>113</v>
       </c>
       <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="36"/>
-      <c r="B10" s="116" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="117"/>
+      <c r="B10" s="121" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="122"/>
       <c r="D10" s="17" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
       <c r="G10" s="57"/>
-      <c r="H10" s="122" t="s">
-        <v>125</v>
+      <c r="H10" s="69" t="s">
+        <v>116</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="55"/>
       <c r="K10" s="55"/>
       <c r="L10" s="55"/>
       <c r="M10" s="56"/>
-      <c r="N10" s="123" t="s">
-        <v>114</v>
+      <c r="N10" s="70" t="s">
+        <v>105</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="7"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="36"/>
-      <c r="B11" s="116" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="117"/>
+      <c r="B11" s="121" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="122"/>
       <c r="D11" s="17" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="57"/>
-      <c r="H11" s="122" t="s">
-        <v>128</v>
+      <c r="H11" s="69" t="s">
+        <v>119</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="55"/>
       <c r="K11" s="55"/>
       <c r="L11" s="55"/>
       <c r="M11" s="56"/>
-      <c r="N11" s="123" t="s">
-        <v>67</v>
+      <c r="N11" s="70" t="s">
+        <v>58</v>
       </c>
       <c r="O11" s="56"/>
       <c r="P11" s="7"/>
@@ -5209,7 +5348,7 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="36"/>
       <c r="B13" s="36" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C13" s="36"/>
       <c r="D13" s="36"/>
@@ -5229,7 +5368,7 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="36"/>
       <c r="B14" s="43" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -5249,7 +5388,7 @@
     <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="36"/>
       <c r="B15" s="31" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -5269,7 +5408,7 @@
     <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="36"/>
       <c r="B16" s="31" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -5289,7 +5428,7 @@
     <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="36"/>
       <c r="B17" s="31" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -5309,7 +5448,7 @@
     <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="36"/>
       <c r="B18" s="31" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
@@ -5347,7 +5486,7 @@
     <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="36"/>
       <c r="B20" s="36" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
@@ -5367,7 +5506,7 @@
     <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="36"/>
       <c r="B21" s="31" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
@@ -5387,7 +5526,7 @@
     <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="36"/>
       <c r="B22" s="31" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -5407,7 +5546,7 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="36"/>
       <c r="B23" s="31" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C23" s="43"/>
       <c r="D23" s="43"/>
@@ -5642,11 +5781,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
@@ -5655,6 +5789,11 @@
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="O2:P2"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5667,23 +5806,23 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="110" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="115" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="117"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -5698,17 +5837,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -5738,7 +5877,7 @@
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5757,7 +5896,7 @@
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
       <c r="B5" s="31" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
@@ -5793,7 +5932,7 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -5812,7 +5951,7 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
@@ -5831,7 +5970,7 @@
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -5867,7 +6006,7 @@
     <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="36"/>
       <c r="B11" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -5886,7 +6025,7 @@
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="36"/>
       <c r="B12" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -5905,7 +6044,7 @@
     <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="36"/>
       <c r="B13" s="36" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -6297,23 +6436,23 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="110" t="s">
-        <v>139</v>
-      </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="114"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="113" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="114"/>
+      <c r="E1" s="115" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="117"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6328,17 +6467,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6385,23 +6524,23 @@
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
       <c r="B5" s="61" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C5" s="62"/>
       <c r="D5" s="61" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E5" s="62"/>
       <c r="F5" s="61" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I5" s="62"/>
       <c r="J5" s="61" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K5" s="55"/>
       <c r="L5" s="63"/>
@@ -6412,11 +6551,11 @@
     <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6424,11 +6563,11 @@
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6439,11 +6578,11 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E7" s="57"/>
       <c r="F7" s="54">
@@ -6451,11 +6590,11 @@
       </c>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6466,11 +6605,11 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -6478,11 +6617,11 @@
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="54" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6493,11 +6632,11 @@
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -6505,11 +6644,11 @@
       </c>
       <c r="G9" s="57"/>
       <c r="H9" s="17" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I9" s="57"/>
       <c r="J9" s="17" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
@@ -6961,23 +7100,23 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="110" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="112" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="114"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="113" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="114"/>
+      <c r="E1" s="115" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="117"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6985,21 +7124,21 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="120"/>
-      <c r="P1" s="121"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="127"/>
     </row>
     <row r="2" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="92"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="114"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="117"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7007,8 +7146,8 @@
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="69"/>
-      <c r="P2" s="70"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="76"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41"/>
@@ -7052,21 +7191,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="66"/>
       <c r="F5" s="52"/>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I5" s="66"/>
       <c r="J5" s="52"/>
       <c r="K5" s="52"/>
       <c r="L5" s="67"/>
       <c r="M5" s="61" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
@@ -7078,21 +7217,21 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="54" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
@@ -7104,21 +7243,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
       <c r="M7" s="54" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>

--- a/要件定義書.xlsx
+++ b/要件定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA89139-32F6-4FE9-8B10-E2DBE31EE522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF6F814-2669-49B1-A599-C5CCAF14A73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="140">
   <si>
     <t>要件定義</t>
   </si>
@@ -369,28 +369,7 @@
     <t>役割</t>
   </si>
   <si>
-    <t>一般ユーザー</t>
-  </si>
-  <si>
-    <t>見積作成、申請</t>
-  </si>
-  <si>
-    <t>承認者</t>
-  </si>
-  <si>
-    <t>見積の承認・差戻し</t>
-  </si>
-  <si>
-    <t>マスタ管理者</t>
-  </si>
-  <si>
-    <t>マスタ管理</t>
-  </si>
-  <si>
     <t>管理者</t>
-  </si>
-  <si>
-    <t>ユーザー管理、マスタ管理、進捗確認</t>
   </si>
   <si>
     <t>非機能要件</t>
@@ -788,6 +767,56 @@
     <t>渡辺のぞみ</t>
     <rPh sb="0" eb="2">
       <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用応募</t>
+    <rPh sb="0" eb="4">
+      <t>サイヨウオウボ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一般</t>
+    <rPh sb="0" eb="2">
+      <t>イッパン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュールカレンダー</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接日・担当者登録、面接希望者状況一覧閲覧</t>
+    <rPh sb="0" eb="3">
+      <t>メンセツビ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>メンセツキボウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>エツラン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -2050,7 +2079,7 @@
       <c r="B6" s="72"/>
       <c r="C6" s="73"/>
       <c r="D6" s="74" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E6" s="74"/>
       <c r="F6" s="74"/>
@@ -2150,7 +2179,7 @@
       </c>
       <c r="G11" s="76"/>
       <c r="H11" s="77" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I11" s="78"/>
       <c r="J11" s="78"/>
@@ -3761,7 +3790,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -3830,7 +3859,7 @@
     <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
       <c r="B5" s="118" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C5" s="118"/>
       <c r="D5" s="118"/>
@@ -3866,7 +3895,7 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -3921,7 +3950,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3995,7 +4024,7 @@
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="36"/>
       <c r="B14" s="112" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C14" s="112"/>
       <c r="D14" s="112"/>
@@ -4014,7 +4043,7 @@
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="36"/>
       <c r="B15" s="112" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C15" s="112"/>
       <c r="D15" s="112"/>
@@ -4033,7 +4062,7 @@
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="36"/>
       <c r="B16" s="112" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C16" s="112"/>
       <c r="D16" s="112"/>
@@ -4122,7 +4151,7 @@
     <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4401,8 +4430,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B23C175-7738-42CA-A6BE-4E914D9B5EA0}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="80" t="s">
@@ -4426,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="40">
-        <v>46001</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
@@ -4533,11 +4565,11 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="121" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="C7" s="122"/>
       <c r="D7" s="54" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -4554,11 +4586,11 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
       <c r="B8" s="121" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="C8" s="122"/>
       <c r="D8" s="54" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="55"/>
@@ -4574,41 +4606,37 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
-      <c r="B9" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
+      <c r="B9" s="121" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="122"/>
+      <c r="D9" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
       <c r="H9" s="52"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="36"/>
-      <c r="B10" s="121" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="57"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
@@ -4633,37 +4661,37 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="36"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="36"/>
@@ -4752,37 +4780,37 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="36"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="36"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="36"/>
@@ -4818,56 +4846,56 @@
       <c r="N22" s="44"/>
       <c r="O22" s="44"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="36"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-    </row>
-    <row r="24" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
+    <row r="23" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="47"/>
+      <c r="O25" s="47"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8"/>
@@ -4922,7 +4950,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
+      <c r="B29" s="47"/>
       <c r="C29" s="47"/>
       <c r="D29" s="47"/>
       <c r="E29" s="47"/>
@@ -4939,20 +4967,20 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8"/>
@@ -5022,27 +5050,10 @@
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:K1"/>
@@ -5071,7 +5082,7 @@
       </c>
       <c r="D1" s="114"/>
       <c r="E1" s="115" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F1" s="116"/>
       <c r="G1" s="116"/>
@@ -5136,7 +5147,7 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5174,17 +5185,17 @@
     <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="36"/>
       <c r="B6" s="119" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C6" s="120"/>
       <c r="D6" s="50" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
       <c r="G6" s="22"/>
       <c r="H6" s="50" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I6" s="51"/>
       <c r="J6" s="51"/>
@@ -5192,7 +5203,7 @@
       <c r="L6" s="52"/>
       <c r="M6" s="67"/>
       <c r="N6" s="50" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="O6" s="56"/>
       <c r="P6" s="7"/>
@@ -5200,17 +5211,17 @@
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="121" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C7" s="122"/>
       <c r="D7" s="54" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
       <c r="G7" s="56"/>
       <c r="H7" s="69" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="55"/>
@@ -5218,7 +5229,7 @@
       <c r="L7" s="55"/>
       <c r="M7" s="56"/>
       <c r="N7" s="70" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="O7" s="56"/>
       <c r="P7" s="7"/>
@@ -5226,17 +5237,17 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
       <c r="B8" s="121" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C8" s="122"/>
       <c r="D8" s="54" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="55"/>
       <c r="G8" s="56"/>
       <c r="H8" s="69" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="55"/>
@@ -5244,7 +5255,7 @@
       <c r="L8" s="55"/>
       <c r="M8" s="56"/>
       <c r="N8" s="70" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="O8" s="56"/>
       <c r="P8" s="7"/>
@@ -5252,17 +5263,17 @@
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
       <c r="B9" s="121" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C9" s="122"/>
       <c r="D9" s="54" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="55"/>
       <c r="G9" s="56"/>
       <c r="H9" s="69" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="55"/>
@@ -5270,7 +5281,7 @@
       <c r="L9" s="55"/>
       <c r="M9" s="56"/>
       <c r="N9" s="70" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="O9" s="56"/>
       <c r="P9" s="7"/>
@@ -5278,17 +5289,17 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="36"/>
       <c r="B10" s="121" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C10" s="122"/>
       <c r="D10" s="17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
       <c r="G10" s="57"/>
       <c r="H10" s="69" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="55"/>
@@ -5296,7 +5307,7 @@
       <c r="L10" s="55"/>
       <c r="M10" s="56"/>
       <c r="N10" s="70" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="7"/>
@@ -5304,17 +5315,17 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="36"/>
       <c r="B11" s="121" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C11" s="122"/>
       <c r="D11" s="17" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="57"/>
       <c r="H11" s="69" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="55"/>
@@ -5322,7 +5333,7 @@
       <c r="L11" s="55"/>
       <c r="M11" s="56"/>
       <c r="N11" s="70" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O11" s="56"/>
       <c r="P11" s="7"/>
@@ -5348,7 +5359,7 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="36"/>
       <c r="B13" s="36" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C13" s="36"/>
       <c r="D13" s="36"/>
@@ -5368,7 +5379,7 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="36"/>
       <c r="B14" s="43" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -5388,7 +5399,7 @@
     <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="36"/>
       <c r="B15" s="31" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C15" s="43"/>
       <c r="D15" s="43"/>
@@ -5408,7 +5419,7 @@
     <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="36"/>
       <c r="B16" s="31" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C16" s="43"/>
       <c r="D16" s="43"/>
@@ -5428,7 +5439,7 @@
     <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="36"/>
       <c r="B17" s="31" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -5448,7 +5459,7 @@
     <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="36"/>
       <c r="B18" s="31" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
@@ -5486,7 +5497,7 @@
     <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="36"/>
       <c r="B20" s="36" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
@@ -5506,7 +5517,7 @@
     <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="36"/>
       <c r="B21" s="31" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
@@ -5526,7 +5537,7 @@
     <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="36"/>
       <c r="B22" s="31" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -5546,7 +5557,7 @@
     <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="36"/>
       <c r="B23" s="31" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C23" s="43"/>
       <c r="D23" s="43"/>
@@ -5815,7 +5826,7 @@
       </c>
       <c r="D1" s="114"/>
       <c r="E1" s="115" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F1" s="116"/>
       <c r="G1" s="116"/>
@@ -5877,7 +5888,7 @@
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5896,7 +5907,7 @@
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
       <c r="B5" s="31" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
@@ -5932,7 +5943,7 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -5951,7 +5962,7 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
@@ -5970,7 +5981,7 @@
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6006,7 +6017,7 @@
     <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="36"/>
       <c r="B11" s="8" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -6025,7 +6036,7 @@
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="36"/>
       <c r="B12" s="8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -6044,7 +6055,7 @@
     <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="36"/>
       <c r="B13" s="36" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -6441,11 +6452,11 @@
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="113" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D1" s="114"/>
       <c r="E1" s="115" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F1" s="116"/>
       <c r="G1" s="116"/>
@@ -6524,23 +6535,23 @@
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
       <c r="B5" s="61" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C5" s="62"/>
       <c r="D5" s="61" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E5" s="62"/>
       <c r="F5" s="61" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I5" s="62"/>
       <c r="J5" s="61" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="K5" s="55"/>
       <c r="L5" s="63"/>
@@ -6551,11 +6562,11 @@
     <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6563,11 +6574,11 @@
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6578,11 +6589,11 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E7" s="57"/>
       <c r="F7" s="54">
@@ -6590,11 +6601,11 @@
       </c>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6605,11 +6616,11 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -6617,11 +6628,11 @@
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="54" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6632,11 +6643,11 @@
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -6644,11 +6655,11 @@
       </c>
       <c r="G9" s="57"/>
       <c r="H9" s="17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I9" s="57"/>
       <c r="J9" s="17" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
@@ -7105,11 +7116,11 @@
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="113" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D1" s="114"/>
       <c r="E1" s="115" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F1" s="116"/>
       <c r="G1" s="116"/>
@@ -7191,21 +7202,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="66"/>
       <c r="F5" s="52"/>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I5" s="66"/>
       <c r="J5" s="52"/>
       <c r="K5" s="52"/>
       <c r="L5" s="67"/>
       <c r="M5" s="61" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
@@ -7217,21 +7228,21 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="54" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
@@ -7243,21 +7254,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
       <c r="M7" s="54" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>

--- a/要件定義書.xlsx
+++ b/要件定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF6F814-2669-49B1-A599-C5CCAF14A73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AA8856-0F96-4127-B1F0-BE2AAA4EFEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="131">
   <si>
     <t>要件定義</t>
   </si>
@@ -480,15 +480,9 @@
     <t>事前のマスタ登録強化</t>
   </si>
   <si>
-    <t>機能要件</t>
-  </si>
-  <si>
     <t>3-1. 機能一覧</t>
   </si>
   <si>
-    <t>機能ID</t>
-  </si>
-  <si>
     <t>機能名</t>
   </si>
   <si>
@@ -496,60 +490,6 @@
   </si>
   <si>
     <t>利用者</t>
-  </si>
-  <si>
-    <t>F-001</t>
-  </si>
-  <si>
-    <t>見積作成</t>
-  </si>
-  <si>
-    <t>顧客・商品情報を基に見積を作成する</t>
-  </si>
-  <si>
-    <t>営業担当</t>
-  </si>
-  <si>
-    <t>F-002</t>
-  </si>
-  <si>
-    <t>承認ワークフロー</t>
-  </si>
-  <si>
-    <t>申請・承認・差戻しを行うワークフロー</t>
-  </si>
-  <si>
-    <t>営業・管理者</t>
-  </si>
-  <si>
-    <t>F-003</t>
-  </si>
-  <si>
-    <t>過去見積検索</t>
-  </si>
-  <si>
-    <t>過去データを条件検索できる</t>
-  </si>
-  <si>
-    <t>全ユーザー</t>
-  </si>
-  <si>
-    <t>F-004</t>
-  </si>
-  <si>
-    <t>商品マスタ参照</t>
-  </si>
-  <si>
-    <t>マスタ登録された商品情報を参照する</t>
-  </si>
-  <si>
-    <t>F-005</t>
-  </si>
-  <si>
-    <t>ダッシュボード</t>
-  </si>
-  <si>
-    <t>承認状況や進捗を一覧で表示</t>
   </si>
   <si>
     <t>3-2. 機能詳細</t>
@@ -818,6 +758,131 @@
     <rPh sb="19" eb="21">
       <t>エツラン</t>
     </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者登録</t>
+    <rPh sb="0" eb="5">
+      <t>オウボシャトウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者が応募情報を登録</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>オウボジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者状況一覧</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者検索</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者の情報が一覧にて見える・更新ボタンにて面接決定日時の登録</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能要件</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者の検索ができる（入力時に使用）</t>
+    <rPh sb="0" eb="2">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ニュウリョクジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用管理者</t>
+    <rPh sb="0" eb="2">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュール（カレンダー）</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>登録された面接日時をスケジュールカレンダーに反映</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>メンセツニチジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>全ユーザー</t>
     <phoneticPr fontId="13"/>
   </si>
 </sst>
@@ -926,7 +991,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -943,6 +1008,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1282,7 +1353,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1666,6 +1737,36 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2079,7 +2180,7 @@
       <c r="B6" s="72"/>
       <c r="C6" s="73"/>
       <c r="D6" s="74" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E6" s="74"/>
       <c r="F6" s="74"/>
@@ -2179,7 +2280,7 @@
       </c>
       <c r="G11" s="76"/>
       <c r="H11" s="77" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="I11" s="78"/>
       <c r="J11" s="78"/>
@@ -3790,7 +3891,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -3859,7 +3960,7 @@
     <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
       <c r="B5" s="118" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C5" s="118"/>
       <c r="D5" s="118"/>
@@ -3895,7 +3996,7 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -3950,7 +4051,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4024,7 +4125,7 @@
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="36"/>
       <c r="B14" s="112" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C14" s="112"/>
       <c r="D14" s="112"/>
@@ -4043,7 +4144,7 @@
     <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="36"/>
       <c r="B15" s="112" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C15" s="112"/>
       <c r="D15" s="112"/>
@@ -4062,7 +4163,7 @@
     <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="36"/>
       <c r="B16" s="112" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C16" s="112"/>
       <c r="D16" s="112"/>
@@ -4151,7 +4252,7 @@
     <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4458,7 +4559,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4565,11 +4666,11 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="36"/>
       <c r="B7" s="121" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C7" s="122"/>
       <c r="D7" s="54" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -4586,11 +4687,11 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="36"/>
       <c r="B8" s="121" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C8" s="122"/>
       <c r="D8" s="54" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="55"/>
@@ -4611,7 +4712,7 @@
       </c>
       <c r="C9" s="122"/>
       <c r="D9" s="17" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
@@ -5069,10 +5170,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8D2F9E-DCA9-4610-96AE-118D7871E7D7}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="10" max="10" width="10.4140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="80" t="s">
         <v>9</v>
       </c>
@@ -5081,52 +5185,50 @@
         <v>30</v>
       </c>
       <c r="D1" s="114"/>
-      <c r="E1" s="115" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="25" t="s">
+      <c r="E1" s="131" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="25" t="s">
+      <c r="L1" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="123">
-        <v>46001</v>
-      </c>
-      <c r="P1" s="124"/>
-    </row>
-    <row r="2" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="N1" s="123">
+        <v>46260</v>
+      </c>
+      <c r="O1" s="124"/>
+    </row>
+    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="83"/>
       <c r="B2" s="85"/>
       <c r="C2" s="113"/>
       <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
+      <c r="E2" s="116"/>
       <c r="F2" s="116"/>
       <c r="G2" s="116"/>
       <c r="H2" s="116"/>
       <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="29" t="s">
+      <c r="J2" s="117"/>
+      <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="29" t="s">
+      <c r="L2" s="28"/>
+      <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="125"/>
-      <c r="P2" s="126"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N2" s="125"/>
+      <c r="O2" s="126"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -5140,14 +5242,13 @@
       <c r="K3" s="41"/>
       <c r="L3" s="41"/>
       <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="7"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="N3" s="36"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5161,10 +5262,9 @@
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="7"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8"/>
       <c r="B5" s="49"/>
       <c r="C5" s="49"/>
@@ -5178,439 +5278,400 @@
       <c r="K5" s="49"/>
       <c r="L5" s="49"/>
       <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="7"/>
-    </row>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="N5" s="8"/>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="36"/>
-      <c r="B6" s="119" t="s">
+      <c r="B6" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="120"/>
-      <c r="D6" s="50" t="s">
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="50" t="s">
+      <c r="L6" s="56"/>
+      <c r="M6" s="128"/>
+      <c r="N6" s="129"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="36"/>
+      <c r="B7" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L7" s="56"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="36"/>
+      <c r="B8" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="L8" s="56"/>
+      <c r="M8" s="130"/>
+      <c r="N8" s="129"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="36"/>
+      <c r="B9" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="69" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="L9" s="56"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="129"/>
+      <c r="O9" s="7"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="36"/>
+      <c r="B10" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="69" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" s="56"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="129"/>
+      <c r="O10" s="7"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="36"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="36"/>
+      <c r="B12" s="133" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="50" t="s">
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="134"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="36"/>
+      <c r="B13" s="135" t="s">
         <v>94</v>
       </c>
-      <c r="O6" s="56"/>
-      <c r="P6" s="7"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="36"/>
-      <c r="B7" s="121" t="s">
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="36"/>
+      <c r="B14" s="136" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="69" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="O7" s="56"/>
-      <c r="P7" s="7"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="36"/>
-      <c r="B8" s="121" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="122"/>
-      <c r="D8" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="70" t="s">
-        <v>102</v>
-      </c>
-      <c r="O8" s="56"/>
-      <c r="P8" s="7"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="36"/>
-      <c r="B9" s="121" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="122"/>
-      <c r="D9" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="69" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="O9" s="56"/>
-      <c r="P9" s="7"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="36"/>
-      <c r="B10" s="121" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="69" t="s">
-        <v>109</v>
-      </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="O10" s="56"/>
-      <c r="P10" s="7"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="36"/>
-      <c r="B11" s="121" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="122"/>
-      <c r="D11" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="O11" s="56"/>
-      <c r="P11" s="7"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="36"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="7"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="7"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="135"/>
+      <c r="L14" s="135"/>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="7"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="36"/>
-      <c r="B15" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
+      <c r="B15" s="136" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="135"/>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="7"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="36"/>
-      <c r="B16" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
+      <c r="B16" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="135"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="7"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O16" s="7"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="36"/>
-      <c r="B17" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
+      <c r="B17" s="136" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="135"/>
+      <c r="L17" s="135"/>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="7"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="36"/>
-      <c r="B18" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="7"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="7"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="133" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="36"/>
-      <c r="B20" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="60"/>
-      <c r="P20" s="7"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="136" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="135"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="36"/>
-      <c r="B21" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
+      <c r="B21" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="135"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="135"/>
+      <c r="L21" s="135"/>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="7"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="36"/>
-      <c r="B22" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
+      <c r="B22" s="136" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="7"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="36"/>
-      <c r="B23" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="7"/>
-    </row>
-    <row r="24" spans="1:16" ht="26.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="7"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="7"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="7"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="7"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="58"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+      <c r="N25" s="47"/>
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8"/>
       <c r="B26" s="58"/>
       <c r="C26" s="47"/>
@@ -5625,10 +5686,9 @@
       <c r="L26" s="47"/>
       <c r="M26" s="47"/>
       <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="7"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O26" s="7"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="8"/>
       <c r="B27" s="58"/>
       <c r="C27" s="47"/>
@@ -5643,10 +5703,9 @@
       <c r="L27" s="47"/>
       <c r="M27" s="47"/>
       <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="7"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="8"/>
       <c r="B28" s="58"/>
       <c r="C28" s="47"/>
@@ -5661,12 +5720,11 @@
       <c r="L28" s="47"/>
       <c r="M28" s="47"/>
       <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
-      <c r="P28" s="7"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O28" s="7"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
+      <c r="B29" s="47"/>
       <c r="C29" s="47"/>
       <c r="D29" s="47"/>
       <c r="E29" s="47"/>
@@ -5679,28 +5737,26 @@
       <c r="L29" s="47"/>
       <c r="M29" s="47"/>
       <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="7"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O29" s="7"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="7"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="7"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -5715,10 +5771,9 @@
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="7"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O31" s="7"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -5733,10 +5788,9 @@
       <c r="L32" s="8"/>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="7"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O32" s="7"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -5751,10 +5805,9 @@
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="7"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -5769,42 +5822,16 @@
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="7"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="7"/>
+      <c r="O34" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B11:C11"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:K2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6452,7 +6479,7 @@
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="113" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D1" s="114"/>
       <c r="E1" s="115" t="s">
@@ -7116,7 +7143,7 @@
       </c>
       <c r="B1" s="82"/>
       <c r="C1" s="113" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="D1" s="114"/>
       <c r="E1" s="115" t="s">

--- a/要件定義書.xlsx
+++ b/要件定義書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AA8856-0F96-4127-B1F0-BE2AAA4EFEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07931CFB-2907-4FE0-9FE0-14D927A37135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="129">
   <si>
     <t>要件定義</t>
   </si>
@@ -150,6 +150,579 @@
   </si>
   <si>
     <t>1-4. 現状（As-Is）</t>
+  </si>
+  <si>
+    <t>1-5. 改善後の姿（To-Be）</t>
+  </si>
+  <si>
+    <t>利用者・権限</t>
+  </si>
+  <si>
+    <t>2-1. 利用者区分</t>
+  </si>
+  <si>
+    <t>利用者区分</t>
+  </si>
+  <si>
+    <t>役割</t>
+  </si>
+  <si>
+    <t>管理者</t>
+  </si>
+  <si>
+    <t>非機能要件</t>
+  </si>
+  <si>
+    <t>4-1. 性能要件</t>
+  </si>
+  <si>
+    <t>・  1,000件の見積データに対し検索応答時間 1 秒以内</t>
+  </si>
+  <si>
+    <t>4-2. セキュリティ要件</t>
+  </si>
+  <si>
+    <t>・  権限管理の実装</t>
+  </si>
+  <si>
+    <t>・  通信経路の HTTPS 暗号化</t>
+  </si>
+  <si>
+    <t>4-3. 可用性</t>
+  </si>
+  <si>
+    <t>・月間稼働率 99.5%以上</t>
+  </si>
+  <si>
+    <t>・システムメンテナンスは深夜帯に実施</t>
+  </si>
+  <si>
+    <t>データ項目定義</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>データ型</t>
+  </si>
+  <si>
+    <t>桁数</t>
+  </si>
+  <si>
+    <t>必須項目</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>顧客名</t>
+  </si>
+  <si>
+    <t>文字列</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>全角対応</t>
+  </si>
+  <si>
+    <t>電話番号</t>
+  </si>
+  <si>
+    <t>ハイフン許容</t>
+  </si>
+  <si>
+    <t>商品コード</t>
+  </si>
+  <si>
+    <t>マスタ参照</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>数値</t>
+  </si>
+  <si>
+    <t>1～99999</t>
+  </si>
+  <si>
+    <t>リスク・課題</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>影響</t>
+  </si>
+  <si>
+    <t>対策</t>
+  </si>
+  <si>
+    <t>承認フローの遅延</t>
+  </si>
+  <si>
+    <t>業務遅延</t>
+  </si>
+  <si>
+    <t>通知機能で抑制</t>
+  </si>
+  <si>
+    <t>マスタ整備不足</t>
+  </si>
+  <si>
+    <t>誤入力発生</t>
+  </si>
+  <si>
+    <t>事前のマスタ登録強化</t>
+  </si>
+  <si>
+    <t>3-1. 機能一覧</t>
+  </si>
+  <si>
+    <t>機能名</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>利用者</t>
+  </si>
+  <si>
+    <t>3-2. 機能詳細</t>
+  </si>
+  <si>
+    <t>F-001 見積作成</t>
+  </si>
+  <si>
+    <t>・  顧客情報（顧客名・担当者・住所）の入力</t>
+  </si>
+  <si>
+    <t>・  商品の検索・追加、数量・単価の登録</t>
+  </si>
+  <si>
+    <t>・   自動計算機能（小計・税額・合計）</t>
+  </si>
+  <si>
+    <t>・  PDF 出力、メール送付機能</t>
+  </si>
+  <si>
+    <t>F-002 承認ワークフロー</t>
+  </si>
+  <si>
+    <t>・  申請→承認→確定の3ステップ</t>
+  </si>
+  <si>
+    <t>・   差戻し理由の記入を必須化</t>
+  </si>
+  <si>
+    <t>・   承認時メール通知を自動送信</t>
+  </si>
+  <si>
+    <t>第5章</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第6章</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用管理システム</t>
+    <rPh sb="0" eb="4">
+      <t>サイヨウカンリ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺 のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接希望者数の増加に伴い、アクション必要数が増加し面接日時決定までの時間の遅れや、対応する人数を増員させることで発生する引継ぎ時間の効率化が必要であったため。</t>
+    <rPh sb="0" eb="6">
+      <t>メンセツキボウシャスウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ヒツヨウスウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="25" eb="31">
+      <t>メンセツニチジケッテイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ニンズウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ゾウイン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>ヒキツ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>コウリツカ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>これらの課題を解消するため、見える化された採用管理システムの構築が必要となった。</t>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>本システムの導入により、採用数の増加に向けたアクションの見える化を実現し、情報共有時間の効率化・面接日程設定までの時間短縮による面接設定件数の増加・採用数の増加を図る。</t>
+    <rPh sb="37" eb="43">
+      <t>ジョウホウキョウユウジカン</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>コウリツカ</t>
+    </rPh>
+    <rPh sb="48" eb="52">
+      <t>メンセツニッテイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="66" eb="70">
+      <t>セッテイケンスウ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>サイヨウスウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接希望者一覧</t>
+    <rPh sb="0" eb="5">
+      <t>メンセツキボウシャ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接日時設定による対応結果（日時・担当者）の閲覧</t>
+    <rPh sb="0" eb="4">
+      <t>メンセツニチジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュール（カレンダー）への反映</t>
+    <rPh sb="15" eb="17">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接決定時、担当者へのメール配信</t>
+    <rPh sb="0" eb="5">
+      <t>メンセツケッテイジ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハイシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用応募</t>
+    <rPh sb="0" eb="4">
+      <t>サイヨウオウボ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一般</t>
+    <rPh sb="0" eb="2">
+      <t>イッパン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュールカレンダー</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接日・担当者登録、面接希望者状況一覧閲覧</t>
+    <rPh sb="0" eb="3">
+      <t>メンセツビ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>メンセツキボウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者登録</t>
+    <rPh sb="0" eb="5">
+      <t>オウボシャトウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者が応募情報を登録</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>オウボジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者状況一覧</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者検索</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者の情報が一覧にて見える・更新ボタンにて面接決定日時の登録</t>
+    <rPh sb="0" eb="3">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能要件</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募者の検索ができる（入力時に使用）</t>
+    <rPh sb="0" eb="2">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ニュウリョクジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用管理者</t>
+    <rPh sb="0" eb="2">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュール（カレンダー）</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>登録された面接日時をスケジュールカレンダーに反映</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>メンセツニチジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>全ユーザー</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>個々の情報として面接日等閲覧可</t>
+    </r>
+    <rPh sb="2" eb="7">
+      <t>ココノジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナド</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <r>
@@ -171,26 +744,24 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>担当者ごとに</t>
+      <t>個々に対するアクションとなり、全体としての進捗が見えにくい</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Excel </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>で見積台帳を管理</t>
-    </r>
+    <rPh sb="2" eb="4">
+      <t>ココ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <r>
@@ -212,8 +783,45 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>バージョン管理がされておらず、最新版が不明確</t>
+      <t>面接日等設定連絡の遅れや、面接日が先</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>伸ばしになるケースも</t>
+    </r>
+    <rPh sb="2" eb="4">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>レンラク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>メンセツヒ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <r>
@@ -235,8 +843,18 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>承認プロセスがメールや口頭ベースで非効率</t>
+      <t>面接設定までの時間の短縮</t>
     </r>
+    <rPh sb="2" eb="6">
+      <t>メンセツセッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <r>
@@ -253,16 +871,37 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
         <charset val="128"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>誤入力による差し戻しが頻発</t>
+      <t>問い合わせのあった応募者を一覧（面接設定日入り）で閲覧できるため</t>
     </r>
-  </si>
-  <si>
-    <t>1-5. 改善後の姿（To-Be）</t>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>セッテイビ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <r>
@@ -271,618 +910,29 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>面接未設定の人を一覧でわかりやすくし、全体で進捗把握の強化</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>システム上で統一された見積フォームを使用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>承認フローをワークフロー化し遅延を解消</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>過去の見積データを検索・再利用可能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>管理者はダッシュボードで進捗を可視化</t>
-    </r>
-  </si>
-  <si>
-    <t>利用者・権限</t>
-  </si>
-  <si>
-    <t>2-1. 利用者区分</t>
-  </si>
-  <si>
-    <t>利用者区分</t>
-  </si>
-  <si>
-    <t>役割</t>
-  </si>
-  <si>
-    <t>管理者</t>
-  </si>
-  <si>
-    <t>非機能要件</t>
-  </si>
-  <si>
-    <t>4-1. 性能要件</t>
-  </si>
-  <si>
-    <t>・  1,000件の見積データに対し検索応答時間 1 秒以内</t>
-  </si>
-  <si>
-    <t>4-2. セキュリティ要件</t>
-  </si>
-  <si>
-    <t>・  権限管理の実装</t>
-  </si>
-  <si>
-    <t>・  通信経路の HTTPS 暗号化</t>
-  </si>
-  <si>
-    <t>4-3. 可用性</t>
-  </si>
-  <si>
-    <t>・月間稼働率 99.5%以上</t>
-  </si>
-  <si>
-    <t>・システムメンテナンスは深夜帯に実施</t>
-  </si>
-  <si>
-    <t>データ項目定義</t>
-  </si>
-  <si>
-    <t>項目名</t>
-  </si>
-  <si>
-    <t>データ型</t>
-  </si>
-  <si>
-    <t>桁数</t>
-  </si>
-  <si>
-    <t>必須項目</t>
-  </si>
-  <si>
-    <t>備考</t>
-  </si>
-  <si>
-    <t>顧客名</t>
-  </si>
-  <si>
-    <t>文字列</t>
-  </si>
-  <si>
-    <t>必須</t>
-  </si>
-  <si>
-    <t>全角対応</t>
-  </si>
-  <si>
-    <t>電話番号</t>
-  </si>
-  <si>
-    <t>ハイフン許容</t>
-  </si>
-  <si>
-    <t>商品コード</t>
-  </si>
-  <si>
-    <t>マスタ参照</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>数値</t>
-  </si>
-  <si>
-    <t>1～99999</t>
-  </si>
-  <si>
-    <t>リスク・課題</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>影響</t>
-  </si>
-  <si>
-    <t>対策</t>
-  </si>
-  <si>
-    <t>承認フローの遅延</t>
-  </si>
-  <si>
-    <t>業務遅延</t>
-  </si>
-  <si>
-    <t>通知機能で抑制</t>
-  </si>
-  <si>
-    <t>マスタ整備不足</t>
-  </si>
-  <si>
-    <t>誤入力発生</t>
-  </si>
-  <si>
-    <t>事前のマスタ登録強化</t>
-  </si>
-  <si>
-    <t>3-1. 機能一覧</t>
-  </si>
-  <si>
-    <t>機能名</t>
-  </si>
-  <si>
-    <t>概要</t>
-  </si>
-  <si>
-    <t>利用者</t>
-  </si>
-  <si>
-    <t>3-2. 機能詳細</t>
-  </si>
-  <si>
-    <t>F-001 見積作成</t>
-  </si>
-  <si>
-    <t>・  顧客情報（顧客名・担当者・住所）の入力</t>
-  </si>
-  <si>
-    <t>・  商品の検索・追加、数量・単価の登録</t>
-  </si>
-  <si>
-    <t>・   自動計算機能（小計・税額・合計）</t>
-  </si>
-  <si>
-    <t>・  PDF 出力、メール送付機能</t>
-  </si>
-  <si>
-    <t>F-002 承認ワークフロー</t>
-  </si>
-  <si>
-    <t>・  申請→承認→確定の3ステップ</t>
-  </si>
-  <si>
-    <t>・   差戻し理由の記入を必須化</t>
-  </si>
-  <si>
-    <t>・   承認時メール通知を自動送信</t>
-  </si>
-  <si>
-    <t>第5章</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>第6章</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>採用管理システム</t>
-    <rPh sb="0" eb="4">
-      <t>サイヨウカンリ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>渡辺 のぞみ</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接希望者数の増加に伴い、アクション必要数が増加し面接日時決定までの時間の遅れや、対応する人数を増員させることで発生する引継ぎ時間の効率化が必要であったため。</t>
-    <rPh sb="0" eb="6">
-      <t>メンセツキボウシャスウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ヒツヨウスウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="25" eb="31">
-      <t>メンセツニチジケッテイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ニンズウ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ゾウイン</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ハッセイ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>ヒキツ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="66" eb="69">
-      <t>コウリツカ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>これらの課題を解消するため、見える化された採用管理システムの構築が必要となった。</t>
-    <rPh sb="14" eb="15">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>サイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>本システムの導入により、採用数の増加に向けたアクションの見える化を実現し、情報共有時間の効率化・面接日程設定までの時間短縮による面接設定件数の増加・採用数の増加を図る。</t>
-    <rPh sb="37" eb="43">
-      <t>ジョウホウキョウユウジカン</t>
-    </rPh>
-    <rPh sb="44" eb="47">
-      <t>コウリツカ</t>
-    </rPh>
-    <rPh sb="48" eb="52">
-      <t>メンセツニッテイ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>タンシュク</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="66" eb="70">
-      <t>セッテイケンスウ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="74" eb="77">
-      <t>サイヨウスウ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="81" eb="82">
-      <t>ハカ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接希望者一覧</t>
-    <rPh sb="0" eb="5">
-      <t>メンセツキボウシャ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
+    <rPh sb="1" eb="6">
+      <t>メンセツミセッテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
       <t>イチラン</t>
     </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接日時設定による対応結果（日時・担当者）の閲覧</t>
-    <rPh sb="0" eb="4">
-      <t>メンセツニチジ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>スケジュール（カレンダー）への反映</t>
-    <rPh sb="15" eb="17">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接決定時、担当者へのメール配信</t>
-    <rPh sb="0" eb="5">
-      <t>メンセツケッテイジ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ハイシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>渡辺のぞみ</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>採用応募</t>
-    <rPh sb="0" eb="4">
-      <t>サイヨウオウボ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>一般</t>
-    <rPh sb="0" eb="2">
-      <t>イッパン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>スケジュールカレンダー</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接日・担当者登録、面接希望者状況一覧閲覧</t>
-    <rPh sb="0" eb="3">
-      <t>メンセツビ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>メンセツキボウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者登録</t>
-    <rPh sb="0" eb="5">
-      <t>オウボシャトウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者が応募情報を登録</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>オウボジョウホウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者状況一覧</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者検索</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者の情報が一覧にて見える・更新ボタンにて面接決定日時の登録</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ケッテイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>機能要件</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者の検索ができる（入力時に使用）</t>
-    <rPh sb="0" eb="2">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ニュウリョクジ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>採用管理者</t>
-    <rPh sb="0" eb="2">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>カンリシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>スケジュール（カレンダー）</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>登録された面接日時をスケジュールカレンダーに反映</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>メンセツニチジ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>全ユーザー</t>
+    <rPh sb="20" eb="22">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>シンチョクハアク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キョウカ</t>
+    </rPh>
     <phoneticPr fontId="13"/>
   </si>
 </sst>
@@ -890,7 +940,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,6 +1039,23 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1353,7 +1420,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1567,51 +1634,135 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1645,42 +1796,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1694,79 +1809,25 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2083,9 +2144,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{762CBF7E-3102-4692-993F-CCBC06E53997}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16">
       <c r="A1" s="8"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2103,7 +2164,7 @@
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:16">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2121,7 +2182,7 @@
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:16">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2139,7 +2200,7 @@
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:16" ht="18.5" thickBot="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2157,7 +2218,7 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:16" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" ht="18.5" thickTop="1">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="10"/>
@@ -2175,47 +2236,47 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="71"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="74" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="73"/>
-      <c r="P6" s="71"/>
-    </row>
-    <row r="7" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="71"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="74" t="s">
+    <row r="6" spans="1:16" ht="39" customHeight="1">
+      <c r="A6" s="96"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="99" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="96"/>
+    </row>
+    <row r="7" spans="1:16" ht="39" customHeight="1">
+      <c r="A7" s="96"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="71"/>
-    </row>
-    <row r="8" spans="1:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="96"/>
+    </row>
+    <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="13"/>
@@ -2233,7 +2294,7 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:16" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:16" ht="18.5" thickTop="1">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2251,7 +2312,7 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2269,91 +2330,91 @@
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="76"/>
-      <c r="H11" s="77" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="78"/>
-      <c r="J11" s="78"/>
-      <c r="K11" s="78"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="94"/>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="75" t="s">
+      <c r="F12" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="76"/>
-      <c r="H12" s="79">
+      <c r="G12" s="92"/>
+      <c r="H12" s="97">
         <v>46265</v>
       </c>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="76"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="94"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -2371,7 +2432,7 @@
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:16">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -2389,7 +2450,7 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:16">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2407,7 +2468,7 @@
       <c r="O17" s="18"/>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:16">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2425,7 +2486,7 @@
       <c r="O18" s="19"/>
       <c r="P18" s="8"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:16">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2443,7 +2504,7 @@
       <c r="O19" s="20"/>
       <c r="P19" s="8"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:16">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2461,7 +2522,7 @@
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
     </row>
-    <row r="21" spans="1:16" ht="29" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:16" ht="29">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2483,22 +2544,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2508,57 +2569,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4686FB26-FBA5-4904-BC7A-25724A1FCDBC}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="86" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="88"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="116"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="93"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="91"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="121"/>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="81"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="119"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="93"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q2" s="120"/>
+      <c r="R2" s="121"/>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2578,433 +2639,433 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="94" t="s">
+      <c r="C4" s="123"/>
+      <c r="D4" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="95"/>
-      <c r="F4" s="94" t="s">
+      <c r="E4" s="123"/>
+      <c r="F4" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="94" t="s">
+      <c r="G4" s="124"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="95"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="123"/>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="101"/>
-      <c r="L5" s="101"/>
-      <c r="M5" s="101"/>
-      <c r="N5" s="101"/>
-      <c r="O5" s="101"/>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="101"/>
-      <c r="R5" s="102"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="106"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="111"/>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="107"/>
-      <c r="K6" s="107"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="107"/>
-      <c r="O6" s="107"/>
-      <c r="P6" s="107"/>
-      <c r="Q6" s="107"/>
-      <c r="R6" s="108"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="100"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="105"/>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="103"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="108"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="100"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="104"/>
+      <c r="R7" s="105"/>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="103"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="107"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="107"/>
-      <c r="M8" s="107"/>
-      <c r="N8" s="107"/>
-      <c r="O8" s="107"/>
-      <c r="P8" s="107"/>
-      <c r="Q8" s="107"/>
-      <c r="R8" s="108"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="100"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="104"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="104"/>
+      <c r="O8" s="104"/>
+      <c r="P8" s="104"/>
+      <c r="Q8" s="104"/>
+      <c r="R8" s="105"/>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="103"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="107"/>
-      <c r="M9" s="107"/>
-      <c r="N9" s="107"/>
-      <c r="O9" s="107"/>
-      <c r="P9" s="107"/>
-      <c r="Q9" s="107"/>
-      <c r="R9" s="108"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="100"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="102"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="104"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="104"/>
+      <c r="P9" s="104"/>
+      <c r="Q9" s="104"/>
+      <c r="R9" s="105"/>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="103"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="107"/>
-      <c r="L10" s="107"/>
-      <c r="M10" s="107"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="107"/>
-      <c r="Q10" s="107"/>
-      <c r="R10" s="108"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="100"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="104"/>
+      <c r="P10" s="104"/>
+      <c r="Q10" s="104"/>
+      <c r="R10" s="105"/>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="103"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="107"/>
-      <c r="K11" s="107"/>
-      <c r="L11" s="107"/>
-      <c r="M11" s="107"/>
-      <c r="N11" s="107"/>
-      <c r="O11" s="107"/>
-      <c r="P11" s="107"/>
-      <c r="Q11" s="107"/>
-      <c r="R11" s="108"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="100"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="104"/>
+      <c r="M11" s="104"/>
+      <c r="N11" s="104"/>
+      <c r="O11" s="104"/>
+      <c r="P11" s="104"/>
+      <c r="Q11" s="104"/>
+      <c r="R11" s="105"/>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="103"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="107"/>
-      <c r="K12" s="107"/>
-      <c r="L12" s="107"/>
-      <c r="M12" s="107"/>
-      <c r="N12" s="107"/>
-      <c r="O12" s="107"/>
-      <c r="P12" s="107"/>
-      <c r="Q12" s="107"/>
-      <c r="R12" s="108"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="100"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="104"/>
+      <c r="N12" s="104"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="104"/>
+      <c r="Q12" s="104"/>
+      <c r="R12" s="105"/>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="103"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="107"/>
-      <c r="M13" s="107"/>
-      <c r="N13" s="107"/>
-      <c r="O13" s="107"/>
-      <c r="P13" s="107"/>
-      <c r="Q13" s="107"/>
-      <c r="R13" s="108"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="100"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="104"/>
+      <c r="K13" s="104"/>
+      <c r="L13" s="104"/>
+      <c r="M13" s="104"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104"/>
+      <c r="R13" s="105"/>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="107"/>
-      <c r="L14" s="107"/>
-      <c r="M14" s="107"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="107"/>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="107"/>
-      <c r="R14" s="108"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="100"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="104"/>
+      <c r="O14" s="104"/>
+      <c r="P14" s="104"/>
+      <c r="Q14" s="104"/>
+      <c r="R14" s="105"/>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="103"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="107"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="107"/>
-      <c r="O15" s="107"/>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="107"/>
-      <c r="R15" s="108"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="100"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="104"/>
+      <c r="N15" s="104"/>
+      <c r="O15" s="104"/>
+      <c r="P15" s="104"/>
+      <c r="Q15" s="104"/>
+      <c r="R15" s="105"/>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="103"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="107"/>
-      <c r="M16" s="107"/>
-      <c r="N16" s="107"/>
-      <c r="O16" s="107"/>
-      <c r="P16" s="107"/>
-      <c r="Q16" s="107"/>
-      <c r="R16" s="108"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="100"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="104"/>
+      <c r="O16" s="104"/>
+      <c r="P16" s="104"/>
+      <c r="Q16" s="104"/>
+      <c r="R16" s="105"/>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="103"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="107"/>
-      <c r="N17" s="107"/>
-      <c r="O17" s="107"/>
-      <c r="P17" s="107"/>
-      <c r="Q17" s="107"/>
-      <c r="R17" s="108"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="100"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="101"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="104"/>
+      <c r="L17" s="104"/>
+      <c r="M17" s="104"/>
+      <c r="N17" s="104"/>
+      <c r="O17" s="104"/>
+      <c r="P17" s="104"/>
+      <c r="Q17" s="104"/>
+      <c r="R17" s="105"/>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="103"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="107"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="107"/>
-      <c r="M18" s="107"/>
-      <c r="N18" s="107"/>
-      <c r="O18" s="107"/>
-      <c r="P18" s="107"/>
-      <c r="Q18" s="107"/>
-      <c r="R18" s="108"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="100"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="104"/>
+      <c r="R18" s="105"/>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="103"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="104"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="107"/>
-      <c r="R19" s="108"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="100"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="101"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="104"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="104"/>
+      <c r="Q19" s="104"/>
+      <c r="R19" s="105"/>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="103"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="103"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107"/>
-      <c r="M20" s="107"/>
-      <c r="N20" s="107"/>
-      <c r="O20" s="107"/>
-      <c r="P20" s="107"/>
-      <c r="Q20" s="107"/>
-      <c r="R20" s="108"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="100"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
+      <c r="N20" s="104"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="104"/>
+      <c r="Q20" s="104"/>
+      <c r="R20" s="105"/>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="103"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="107"/>
-      <c r="N21" s="107"/>
-      <c r="O21" s="107"/>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="108"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="100"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="104"/>
+      <c r="N21" s="104"/>
+      <c r="O21" s="104"/>
+      <c r="P21" s="104"/>
+      <c r="Q21" s="104"/>
+      <c r="R21" s="105"/>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="103"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="107"/>
-      <c r="M22" s="107"/>
-      <c r="N22" s="107"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="107"/>
-      <c r="Q22" s="107"/>
-      <c r="R22" s="108"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="100"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="100"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="104"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="104"/>
+      <c r="N22" s="104"/>
+      <c r="O22" s="104"/>
+      <c r="P22" s="104"/>
+      <c r="Q22" s="104"/>
+      <c r="R22" s="105"/>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3024,7 +3085,7 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:18">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -3044,7 +3105,7 @@
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:18">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3064,7 +3125,7 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:18">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3084,7 +3145,7 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:18">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -3104,7 +3165,7 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:18">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -3124,7 +3185,7 @@
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:18">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -3146,6 +3207,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:O2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:H21"/>
@@ -3154,78 +3287,6 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="I22:R22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:O2"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:R4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3235,26 +3296,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFF7F1E-AE30-4269-AC6F-F8A3C5E0A4BA}">
   <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="80" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -3264,20 +3325,20 @@
       </c>
       <c r="Q1" s="26"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
+    <row r="2" spans="1:17">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3287,7 +3348,7 @@
       </c>
       <c r="Q2" s="30"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17">
       <c r="A3" s="32"/>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -3306,18 +3367,18 @@
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17">
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="109" t="s">
+      <c r="B4" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="111"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="127"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3325,19 +3386,19 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="109" t="s">
+      <c r="K4" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="111"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="127"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17">
       <c r="A5" s="16"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -3356,7 +3417,7 @@
       <c r="P5" s="36"/>
       <c r="Q5" s="36"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17">
       <c r="A6" s="37" t="s">
         <v>19</v>
       </c>
@@ -3387,7 +3448,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17">
       <c r="A7" s="37">
         <v>1.1000000000000001</v>
       </c>
@@ -3418,7 +3479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17">
       <c r="A8" s="37">
         <v>1.2</v>
       </c>
@@ -3449,7 +3510,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:17">
       <c r="A9" s="37">
         <v>1.3</v>
       </c>
@@ -3480,7 +3541,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17">
       <c r="A10" s="37">
         <v>1.4</v>
       </c>
@@ -3511,7 +3572,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:17">
       <c r="A11" s="37">
         <v>1.5</v>
       </c>
@@ -3542,7 +3603,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17">
       <c r="A12" s="37" t="s">
         <v>27</v>
       </c>
@@ -3567,7 +3628,7 @@
       <c r="P12" s="31"/>
       <c r="Q12" s="31"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:17">
       <c r="A13" s="37">
         <v>2.1</v>
       </c>
@@ -3592,7 +3653,7 @@
       <c r="P13" s="31"/>
       <c r="Q13" s="31"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17">
       <c r="A14" s="37">
         <v>2.2000000000000002</v>
       </c>
@@ -3617,7 +3678,7 @@
       <c r="P14" s="31"/>
       <c r="Q14" s="31"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:17">
       <c r="A15" s="37">
         <v>2.2999999999999998</v>
       </c>
@@ -3642,7 +3703,7 @@
       <c r="P15" s="31"/>
       <c r="Q15" s="31"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17">
       <c r="A16" s="37">
         <v>2.4</v>
       </c>
@@ -3667,7 +3728,7 @@
       <c r="P16" s="31"/>
       <c r="Q16" s="31"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17">
       <c r="A17" s="37">
         <v>2.5</v>
       </c>
@@ -3692,7 +3753,7 @@
       <c r="P17" s="31"/>
       <c r="Q17" s="31"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17">
       <c r="A18" s="37" t="s">
         <v>30</v>
       </c>
@@ -3717,7 +3778,7 @@
       <c r="P18" s="31"/>
       <c r="Q18" s="31"/>
     </row>
-    <row r="19" spans="1:17" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" ht="26.5">
       <c r="A19" s="37">
         <v>3.1</v>
       </c>
@@ -3742,7 +3803,7 @@
       <c r="P19" s="38"/>
       <c r="Q19" s="38"/>
     </row>
-    <row r="20" spans="1:17" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" ht="26.5">
       <c r="A20" s="37">
         <v>3.2</v>
       </c>
@@ -3767,7 +3828,7 @@
       <c r="P20" s="38"/>
       <c r="Q20" s="38"/>
     </row>
-    <row r="21" spans="1:17" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" ht="26.5">
       <c r="A21" s="37">
         <v>3.3</v>
       </c>
@@ -3792,7 +3853,7 @@
       <c r="P21" s="38"/>
       <c r="Q21" s="38"/>
     </row>
-    <row r="22" spans="1:17" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" ht="26.5">
       <c r="A22" s="38"/>
       <c r="B22" s="16"/>
       <c r="C22" s="7"/>
@@ -3811,7 +3872,7 @@
       <c r="P22" s="38"/>
       <c r="Q22" s="38"/>
     </row>
-    <row r="23" spans="1:17" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" ht="26.5">
       <c r="A23" s="38"/>
       <c r="B23" s="39"/>
       <c r="C23" s="38"/>
@@ -3830,7 +3891,7 @@
       <c r="P23" s="38"/>
       <c r="Q23" s="38"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17">
       <c r="A24" s="7"/>
       <c r="B24" s="16"/>
       <c r="C24" s="7"/>
@@ -3863,35 +3924,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A53200-138B-4730-BC3C-8EB91F016A0A}">
-  <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:O33"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:15" ht="20">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="113" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="115" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="88"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -3900,18 +3961,18 @@
         <v>46260</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
+    <row r="2" spans="1:15" ht="20">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="88"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -3921,7 +3982,7 @@
       </c>
       <c r="O2" s="30"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -3938,7 +3999,7 @@
       <c r="N3" s="41"/>
       <c r="O3" s="41"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
         <v>33</v>
@@ -3957,46 +4018,46 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="118" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="B5" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="130"/>
+      <c r="N5" s="130"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15">
       <c r="A6" s="36"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="118"/>
-      <c r="N6" s="118"/>
+      <c r="B6" s="130"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -4012,7 +4073,7 @@
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
@@ -4029,7 +4090,7 @@
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="s">
         <v>34</v>
@@ -4048,10 +4109,10 @@
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4067,7 +4128,7 @@
       <c r="N10" s="8"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -4084,7 +4145,7 @@
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="36" t="s">
         <v>35</v>
@@ -4103,117 +4164,117 @@
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="112"/>
-      <c r="N13" s="112"/>
-      <c r="O13" s="112"/>
-    </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C13" s="128"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+    </row>
+    <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="112" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="112"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="112"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="112"/>
-    </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="128" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="128"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="128"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="128"/>
+      <c r="M14" s="128"/>
+      <c r="N14" s="128"/>
+      <c r="O14" s="128"/>
+    </row>
+    <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="112" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="112"/>
-      <c r="D15" s="112"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="112"/>
-      <c r="H15" s="112"/>
-      <c r="I15" s="112"/>
-      <c r="J15" s="112"/>
-      <c r="K15" s="112"/>
-      <c r="L15" s="112"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="112"/>
-    </row>
-    <row r="16" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="128" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="128"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="128"/>
+      <c r="M15" s="128"/>
+      <c r="N15" s="128"/>
+      <c r="O15" s="128"/>
+    </row>
+    <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
-      <c r="B16" s="112" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="112"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="112"/>
-    </row>
-    <row r="17" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="128"/>
+      <c r="O16" s="128"/>
+    </row>
+    <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="112"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
-      <c r="L17" s="112"/>
-      <c r="M17" s="112"/>
-      <c r="N17" s="112"/>
-      <c r="O17" s="112"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="128"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="128"/>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="112"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="112"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="112"/>
-      <c r="O18" s="112"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="128"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="128"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="128"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="128"/>
+      <c r="N18" s="128"/>
+      <c r="O18" s="128"/>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -4230,7 +4291,7 @@
       <c r="N19" s="42"/>
       <c r="O19" s="42"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="43" t="s">
         <v>37</v>
@@ -4249,10 +4310,10 @@
       <c r="N20" s="44"/>
       <c r="O20" s="44"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4268,7 +4329,7 @@
       <c r="N21" s="44"/>
       <c r="O21" s="44"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15">
       <c r="A22" s="36"/>
       <c r="B22" s="43"/>
       <c r="C22" s="44"/>
@@ -4285,7 +4346,7 @@
       <c r="N22" s="44"/>
       <c r="O22" s="44"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" ht="26.5">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -4302,7 +4363,7 @@
       <c r="N23" s="45"/>
       <c r="O23" s="45"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
         <v>38</v>
@@ -4321,10 +4382,10 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4340,10 +4401,10 @@
       <c r="N25" s="47"/>
       <c r="O25" s="47"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4359,10 +4420,10 @@
       <c r="N26" s="47"/>
       <c r="O26" s="47"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4378,17 +4439,14 @@
       <c r="N27" s="47"/>
       <c r="O27" s="47"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="46" t="s">
-        <v>42</v>
-      </c>
+      <c r="B28" s="47"/>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
       <c r="F28" s="47"/>
       <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
       <c r="I28" s="47"/>
       <c r="J28" s="47"/>
       <c r="K28" s="47"/>
@@ -4397,27 +4455,29 @@
       <c r="N28" s="47"/>
       <c r="O28" s="47"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="8" t="s">
-        <v>43</v>
+      <c r="B30" s="48" t="s">
+        <v>127</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4433,10 +4493,10 @@
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4452,10 +4512,10 @@
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4471,11 +4531,9 @@
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15">
       <c r="A33" s="8"/>
-      <c r="B33" s="48" t="s">
-        <v>46</v>
-      </c>
+      <c r="B33" s="48"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -4489,25 +4547,6 @@
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="8"/>
-      <c r="B34" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4532,34 +4571,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B23C175-7738-42CA-A6BE-4E914D9B5EA0}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:15" ht="20">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="113" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="115" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="129" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="88"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4568,18 +4607,18 @@
         <v>46260</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
+    <row r="2" spans="1:15" ht="20">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="88"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4589,7 +4628,7 @@
       </c>
       <c r="O2" s="30"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -4606,10 +4645,10 @@
       <c r="N3" s="41"/>
       <c r="O3" s="41"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4625,7 +4664,7 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="49"/>
       <c r="C5" s="49"/>
@@ -4642,14 +4681,14 @@
       <c r="N5" s="49"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
-      <c r="B6" s="119" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="120"/>
+      <c r="B6" s="133" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="134"/>
       <c r="D6" s="50" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -4663,14 +4702,14 @@
       <c r="N6" s="49"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15">
       <c r="A7" s="36"/>
-      <c r="B7" s="121" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="122"/>
+      <c r="B7" s="131" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="132"/>
       <c r="D7" s="54" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -4684,14 +4723,14 @@
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="121" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="122"/>
+      <c r="B8" s="131" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="132"/>
       <c r="D8" s="54" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="55"/>
@@ -4705,14 +4744,14 @@
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15">
       <c r="A9" s="36"/>
-      <c r="B9" s="121" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="122"/>
+      <c r="B9" s="131" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="132"/>
       <c r="D9" s="17" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
@@ -4726,7 +4765,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -4743,7 +4782,7 @@
       <c r="N10" s="8"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -4760,7 +4799,7 @@
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
@@ -4777,7 +4816,7 @@
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
@@ -4794,7 +4833,7 @@
       <c r="N13" s="44"/>
       <c r="O13" s="44"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="44"/>
       <c r="C14" s="44"/>
@@ -4811,7 +4850,7 @@
       <c r="N14" s="44"/>
       <c r="O14" s="44"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="44"/>
       <c r="C15" s="44"/>
@@ -4828,7 +4867,7 @@
       <c r="N15" s="44"/>
       <c r="O15" s="44"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15">
       <c r="A16" s="36"/>
       <c r="B16" s="44"/>
       <c r="C16" s="44"/>
@@ -4845,7 +4884,7 @@
       <c r="N16" s="44"/>
       <c r="O16" s="44"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="44"/>
       <c r="C17" s="44"/>
@@ -4862,7 +4901,7 @@
       <c r="N17" s="44"/>
       <c r="O17" s="44"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="44"/>
       <c r="C18" s="44"/>
@@ -4879,7 +4918,7 @@
       <c r="N18" s="44"/>
       <c r="O18" s="44"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
@@ -4896,7 +4935,7 @@
       <c r="N19" s="42"/>
       <c r="O19" s="42"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="43"/>
       <c r="C20" s="44"/>
@@ -4913,7 +4952,7 @@
       <c r="N20" s="44"/>
       <c r="O20" s="44"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43"/>
       <c r="C21" s="44"/>
@@ -4930,7 +4969,7 @@
       <c r="N21" s="44"/>
       <c r="O21" s="44"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15">
       <c r="A22" s="36"/>
       <c r="B22" s="43"/>
       <c r="C22" s="44"/>
@@ -4947,7 +4986,7 @@
       <c r="N22" s="44"/>
       <c r="O22" s="44"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" ht="26.5">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -4964,7 +5003,7 @@
       <c r="N23" s="45"/>
       <c r="O23" s="45"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -4981,7 +5020,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58"/>
       <c r="C25" s="47"/>
@@ -4998,7 +5037,7 @@
       <c r="N25" s="47"/>
       <c r="O25" s="47"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="58"/>
       <c r="C26" s="47"/>
@@ -5015,7 +5054,7 @@
       <c r="N26" s="47"/>
       <c r="O26" s="47"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58"/>
       <c r="C27" s="47"/>
@@ -5032,7 +5071,7 @@
       <c r="N27" s="47"/>
       <c r="O27" s="47"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="58"/>
       <c r="C28" s="47"/>
@@ -5049,7 +5088,7 @@
       <c r="N28" s="47"/>
       <c r="O28" s="47"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="47"/>
       <c r="C29" s="47"/>
@@ -5066,7 +5105,7 @@
       <c r="N29" s="47"/>
       <c r="O29" s="47"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -5083,7 +5122,7 @@
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -5100,7 +5139,7 @@
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -5117,7 +5156,7 @@
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -5134,7 +5173,7 @@
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -5171,53 +5210,53 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8D2F9E-DCA9-4610-96AE-118D7871E7D7}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="10" max="10" width="10.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:15" ht="20">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="113" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="131" t="s">
-        <v>125</v>
-      </c>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="132"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="72" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="73"/>
       <c r="K1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="123">
+      <c r="N1" s="85">
         <v>46260</v>
       </c>
-      <c r="O1" s="124"/>
-    </row>
-    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="117"/>
+      <c r="O1" s="86"/>
+    </row>
+    <row r="2" spans="1:15" ht="20">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="88"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5225,10 +5264,10 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="125"/>
-      <c r="O2" s="126"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="N2" s="89"/>
+      <c r="O2" s="90"/>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -5245,10 +5284,10 @@
       <c r="N3" s="36"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5264,7 +5303,7 @@
       <c r="N4" s="8"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="49"/>
       <c r="C5" s="49"/>
@@ -5281,15 +5320,15 @@
       <c r="N5" s="8"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
       <c r="B6" s="50" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="50" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
@@ -5297,22 +5336,22 @@
       <c r="I6" s="52"/>
       <c r="J6" s="67"/>
       <c r="K6" s="50" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="L6" s="56"/>
-      <c r="M6" s="128"/>
-      <c r="N6" s="129"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="36"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5320,22 +5359,22 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="129"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="36"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5343,22 +5382,22 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L8" s="56"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="129"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="36"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5366,22 +5405,22 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L9" s="56"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="129"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="36"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="69" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="55"/>
@@ -5389,14 +5428,14 @@
       <c r="I10" s="55"/>
       <c r="J10" s="56"/>
       <c r="K10" s="70" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="L10" s="56"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="129"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="36"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -5413,214 +5452,214 @@
       <c r="N11" s="36"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15">
       <c r="A12" s="36"/>
-      <c r="B12" s="133" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="134"/>
-      <c r="I12" s="134"/>
-      <c r="J12" s="133"/>
-      <c r="K12" s="133"/>
-      <c r="L12" s="133"/>
+      <c r="B12" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="74"/>
       <c r="M12" s="36"/>
       <c r="N12" s="36"/>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15">
       <c r="A13" s="36"/>
-      <c r="B13" s="135" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
+      <c r="B13" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="76"/>
+      <c r="L13" s="76"/>
       <c r="M13" s="43"/>
       <c r="N13" s="43"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15">
       <c r="A14" s="36"/>
-      <c r="B14" s="136" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="135"/>
-      <c r="K14" s="135"/>
-      <c r="L14" s="135"/>
+      <c r="B14" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15">
       <c r="A15" s="36"/>
-      <c r="B15" s="136" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="135"/>
+      <c r="B15" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15">
       <c r="A16" s="36"/>
-      <c r="B16" s="136" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
+      <c r="B16" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15">
       <c r="A17" s="36"/>
-      <c r="B17" s="136" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="135"/>
-      <c r="D17" s="135"/>
-      <c r="E17" s="135"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="135"/>
-      <c r="L17" s="135"/>
+      <c r="B17" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="76"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="76"/>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="135"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
-      <c r="L18" s="135"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="76"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15">
       <c r="A19" s="36"/>
-      <c r="B19" s="133" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="137"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="137"/>
-      <c r="H19" s="137"/>
-      <c r="I19" s="137"/>
-      <c r="J19" s="137"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
+      <c r="B19" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
       <c r="M19" s="60"/>
       <c r="N19" s="60"/>
       <c r="O19" s="7"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15">
       <c r="A20" s="36"/>
-      <c r="B20" s="136" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="135"/>
-      <c r="D20" s="135"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="135"/>
-      <c r="K20" s="135"/>
-      <c r="L20" s="135"/>
+      <c r="B20" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="76"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="76"/>
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15">
       <c r="A21" s="36"/>
-      <c r="B21" s="136" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="135"/>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="135"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="135"/>
-      <c r="J21" s="135"/>
-      <c r="K21" s="135"/>
-      <c r="L21" s="135"/>
+      <c r="B21" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="76"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="76"/>
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15">
       <c r="A22" s="36"/>
-      <c r="B22" s="136" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="135"/>
-      <c r="D22" s="135"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="135"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="135"/>
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
+      <c r="B22" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" ht="26.5">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -5637,7 +5676,7 @@
       <c r="N23" s="45"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -5654,7 +5693,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="7"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58"/>
       <c r="C25" s="47"/>
@@ -5671,7 +5710,7 @@
       <c r="N25" s="47"/>
       <c r="O25" s="7"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="58"/>
       <c r="C26" s="47"/>
@@ -5688,7 +5727,7 @@
       <c r="N26" s="47"/>
       <c r="O26" s="7"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58"/>
       <c r="C27" s="47"/>
@@ -5705,7 +5744,7 @@
       <c r="N27" s="47"/>
       <c r="O27" s="7"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="58"/>
       <c r="C28" s="47"/>
@@ -5722,7 +5761,7 @@
       <c r="N28" s="47"/>
       <c r="O28" s="7"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="47"/>
       <c r="C29" s="47"/>
@@ -5739,7 +5778,7 @@
       <c r="N29" s="47"/>
       <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -5756,7 +5795,7 @@
       <c r="N30" s="8"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -5773,7 +5812,7 @@
       <c r="N31" s="8"/>
       <c r="O31" s="7"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -5790,7 +5829,7 @@
       <c r="N32" s="8"/>
       <c r="O32" s="7"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -5807,7 +5846,7 @@
       <c r="N33" s="8"/>
       <c r="O33" s="7"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -5841,26 +5880,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D678CDCE-2C5A-4AFB-B9CB-39BA46C32C81}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:15" ht="20">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="113" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="115" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="129" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="88"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -5874,18 +5913,18 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
+    <row r="2" spans="1:15" ht="20">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="88"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -5895,7 +5934,7 @@
       </c>
       <c r="O2" s="26"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -5912,10 +5951,10 @@
       <c r="N3" s="41"/>
       <c r="O3" s="41"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5931,10 +5970,10 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="31" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
@@ -5950,7 +5989,7 @@
       <c r="N5" s="31"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
@@ -5967,10 +6006,10 @@
       <c r="N6" s="31"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -5986,10 +6025,10 @@
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
@@ -6005,10 +6044,10 @@
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6024,7 +6063,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
@@ -6041,10 +6080,10 @@
       <c r="N10" s="8"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -6060,10 +6099,10 @@
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="8" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -6079,10 +6118,10 @@
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="36" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -6098,7 +6137,7 @@
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
@@ -6115,7 +6154,7 @@
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
@@ -6132,7 +6171,7 @@
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15">
       <c r="A16" s="36"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -6149,7 +6188,7 @@
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
@@ -6166,7 +6205,7 @@
       <c r="N17" s="43"/>
       <c r="O17" s="43"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
@@ -6183,7 +6222,7 @@
       <c r="N18" s="43"/>
       <c r="O18" s="43"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
@@ -6200,7 +6239,7 @@
       <c r="N19" s="60"/>
       <c r="O19" s="60"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
@@ -6217,7 +6256,7 @@
       <c r="N20" s="43"/>
       <c r="O20" s="43"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
@@ -6234,7 +6273,7 @@
       <c r="N21" s="43"/>
       <c r="O21" s="43"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15">
       <c r="A22" s="36"/>
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
@@ -6251,7 +6290,7 @@
       <c r="N22" s="43"/>
       <c r="O22" s="43"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" ht="26.5">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -6268,7 +6307,7 @@
       <c r="N23" s="45"/>
       <c r="O23" s="45"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6285,7 +6324,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58"/>
       <c r="C25" s="58"/>
@@ -6302,7 +6341,7 @@
       <c r="N25" s="58"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="58"/>
       <c r="C26" s="58"/>
@@ -6319,7 +6358,7 @@
       <c r="N26" s="58"/>
       <c r="O26" s="58"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58"/>
       <c r="C27" s="58"/>
@@ -6336,7 +6375,7 @@
       <c r="N27" s="58"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
@@ -6353,7 +6392,7 @@
       <c r="N28" s="58"/>
       <c r="O28" s="58"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
@@ -6370,7 +6409,7 @@
       <c r="N29" s="58"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -6387,7 +6426,7 @@
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -6404,7 +6443,7 @@
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -6421,7 +6460,7 @@
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -6438,7 +6477,7 @@
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -6471,26 +6510,26 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{140C4B60-E55A-4E72-B14E-C7619F01C68D}">
   <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:15" ht="20">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="115" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="84"/>
+      <c r="E1" s="129" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="88"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6504,18 +6543,18 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
+    <row r="2" spans="1:15" ht="20">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="88"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6525,7 +6564,7 @@
       </c>
       <c r="O2" s="26"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:15">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -6542,7 +6581,7 @@
       <c r="N3" s="41"/>
       <c r="O3" s="41"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36"/>
       <c r="C4" s="8"/>
@@ -6559,26 +6598,26 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="61" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C5" s="62"/>
       <c r="D5" s="61" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E5" s="62"/>
       <c r="F5" s="61" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I5" s="62"/>
       <c r="J5" s="61" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="K5" s="55"/>
       <c r="L5" s="63"/>
@@ -6586,14 +6625,14 @@
       <c r="N5" s="31"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6601,11 +6640,11 @@
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6613,14 +6652,14 @@
       <c r="N6" s="31"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E7" s="57"/>
       <c r="F7" s="54">
@@ -6628,11 +6667,11 @@
       </c>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6640,14 +6679,14 @@
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -6655,11 +6694,11 @@
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="54" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6667,14 +6706,14 @@
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -6682,11 +6721,11 @@
       </c>
       <c r="G9" s="57"/>
       <c r="H9" s="17" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I9" s="57"/>
       <c r="J9" s="17" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="23"/>
@@ -6694,7 +6733,7 @@
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
@@ -6711,7 +6750,7 @@
       <c r="N10" s="8"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -6728,7 +6767,7 @@
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="8"/>
       <c r="C12" s="36"/>
@@ -6745,7 +6784,7 @@
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="36"/>
       <c r="C13" s="43"/>
@@ -6762,7 +6801,7 @@
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
@@ -6779,7 +6818,7 @@
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
@@ -6796,7 +6835,7 @@
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15">
       <c r="A16" s="36"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -6813,7 +6852,7 @@
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
@@ -6830,7 +6869,7 @@
       <c r="N17" s="43"/>
       <c r="O17" s="43"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
@@ -6847,7 +6886,7 @@
       <c r="N18" s="43"/>
       <c r="O18" s="43"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
@@ -6864,7 +6903,7 @@
       <c r="N19" s="60"/>
       <c r="O19" s="60"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
@@ -6881,7 +6920,7 @@
       <c r="N20" s="43"/>
       <c r="O20" s="43"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
@@ -6898,7 +6937,7 @@
       <c r="N21" s="43"/>
       <c r="O21" s="43"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15">
       <c r="A22" s="36"/>
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
@@ -6915,7 +6954,7 @@
       <c r="N22" s="43"/>
       <c r="O22" s="43"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" ht="26.5">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -6932,7 +6971,7 @@
       <c r="N23" s="45"/>
       <c r="O23" s="45"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -6949,7 +6988,7 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58"/>
       <c r="C25" s="58"/>
@@ -6966,7 +7005,7 @@
       <c r="N25" s="58"/>
       <c r="O25" s="58"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="58"/>
       <c r="C26" s="58"/>
@@ -6983,7 +7022,7 @@
       <c r="N26" s="58"/>
       <c r="O26" s="58"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58"/>
       <c r="C27" s="58"/>
@@ -7000,7 +7039,7 @@
       <c r="N27" s="58"/>
       <c r="O27" s="58"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
@@ -7017,7 +7056,7 @@
       <c r="N28" s="58"/>
       <c r="O28" s="58"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
@@ -7034,7 +7073,7 @@
       <c r="N29" s="58"/>
       <c r="O29" s="58"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -7051,7 +7090,7 @@
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -7068,7 +7107,7 @@
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -7085,7 +7124,7 @@
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7102,7 +7141,7 @@
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -7135,26 +7174,26 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B52A5B-90BF-4339-BD21-5A13EC799265}">
   <dimension ref="A1:P34"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="80" t="s">
+    <row r="1" spans="1:16" ht="20">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="113" t="s">
-        <v>104</v>
-      </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="115" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="117"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="84"/>
+      <c r="E1" s="129" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="88"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -7162,21 +7201,21 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="123"/>
-      <c r="P1" s="127"/>
-    </row>
-    <row r="2" spans="1:16" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="83"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="135"/>
+    </row>
+    <row r="2" spans="1:16" ht="20">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="88"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7184,10 +7223,10 @@
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="75"/>
-      <c r="P2" s="76"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="O2" s="91"/>
+      <c r="P2" s="92"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="41"/>
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
@@ -7205,7 +7244,7 @@
       <c r="O3" s="36"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:16">
       <c r="A4" s="8"/>
       <c r="B4" s="36"/>
       <c r="C4" s="8"/>
@@ -7223,85 +7262,85 @@
       <c r="O4" s="8"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16">
       <c r="A5" s="8"/>
       <c r="B5" s="65" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="66"/>
       <c r="F5" s="52"/>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I5" s="66"/>
       <c r="J5" s="52"/>
       <c r="K5" s="52"/>
       <c r="L5" s="67"/>
       <c r="M5" s="61" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16">
       <c r="A6" s="36"/>
       <c r="B6" s="68">
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="54" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16">
       <c r="A7" s="36"/>
       <c r="B7" s="68">
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
       <c r="M7" s="54" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:16">
       <c r="A8" s="36"/>
       <c r="B8" s="68"/>
       <c r="C8" s="54"/>
@@ -7319,7 +7358,7 @@
       <c r="O8" s="56"/>
       <c r="P8" s="7"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:16">
       <c r="A9" s="36"/>
       <c r="B9" s="68"/>
       <c r="C9" s="17"/>
@@ -7337,7 +7376,7 @@
       <c r="O9" s="56"/>
       <c r="P9" s="7"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:16">
       <c r="A10" s="36"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
@@ -7355,7 +7394,7 @@
       <c r="O10" s="36"/>
       <c r="P10" s="7"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:16">
       <c r="A11" s="36"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -7373,7 +7412,7 @@
       <c r="O11" s="36"/>
       <c r="P11" s="7"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:16">
       <c r="A12" s="36"/>
       <c r="B12" s="8"/>
       <c r="C12" s="36"/>
@@ -7391,7 +7430,7 @@
       <c r="O12" s="36"/>
       <c r="P12" s="7"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:16">
       <c r="A13" s="36"/>
       <c r="B13" s="36"/>
       <c r="C13" s="43"/>
@@ -7409,7 +7448,7 @@
       <c r="O13" s="43"/>
       <c r="P13" s="7"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:16">
       <c r="A14" s="36"/>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
@@ -7427,7 +7466,7 @@
       <c r="O14" s="43"/>
       <c r="P14" s="7"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:16">
       <c r="A15" s="36"/>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
@@ -7445,7 +7484,7 @@
       <c r="O15" s="43"/>
       <c r="P15" s="7"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:16">
       <c r="A16" s="36"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -7463,7 +7502,7 @@
       <c r="O16" s="43"/>
       <c r="P16" s="7"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:16">
       <c r="A17" s="36"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
@@ -7481,7 +7520,7 @@
       <c r="O17" s="43"/>
       <c r="P17" s="7"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:16">
       <c r="A18" s="36"/>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
@@ -7499,7 +7538,7 @@
       <c r="O18" s="43"/>
       <c r="P18" s="7"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:16">
       <c r="A19" s="36"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
@@ -7517,7 +7556,7 @@
       <c r="O19" s="60"/>
       <c r="P19" s="7"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:16">
       <c r="A20" s="36"/>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
@@ -7535,7 +7574,7 @@
       <c r="O20" s="43"/>
       <c r="P20" s="7"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:16">
       <c r="A21" s="36"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
@@ -7553,7 +7592,7 @@
       <c r="O21" s="43"/>
       <c r="P21" s="7"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:16">
       <c r="A22" s="36"/>
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
@@ -7571,7 +7610,7 @@
       <c r="O22" s="43"/>
       <c r="P22" s="7"/>
     </row>
-    <row r="23" spans="1:16" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:16" ht="26.5">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -7589,7 +7628,7 @@
       <c r="O23" s="45"/>
       <c r="P23" s="7"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:16">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -7607,7 +7646,7 @@
       <c r="O24" s="8"/>
       <c r="P24" s="7"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:16">
       <c r="A25" s="8"/>
       <c r="B25" s="58"/>
       <c r="C25" s="58"/>
@@ -7625,7 +7664,7 @@
       <c r="O25" s="58"/>
       <c r="P25" s="7"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:16">
       <c r="A26" s="8"/>
       <c r="B26" s="58"/>
       <c r="C26" s="58"/>
@@ -7643,7 +7682,7 @@
       <c r="O26" s="58"/>
       <c r="P26" s="7"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:16">
       <c r="A27" s="8"/>
       <c r="B27" s="58"/>
       <c r="C27" s="58"/>
@@ -7661,7 +7700,7 @@
       <c r="O27" s="58"/>
       <c r="P27" s="7"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:16">
       <c r="A28" s="8"/>
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
@@ -7679,7 +7718,7 @@
       <c r="O28" s="58"/>
       <c r="P28" s="7"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:16">
       <c r="A29" s="8"/>
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
@@ -7697,7 +7736,7 @@
       <c r="O29" s="58"/>
       <c r="P29" s="7"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:16">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -7715,7 +7754,7 @@
       <c r="O30" s="8"/>
       <c r="P30" s="7"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:16">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -7733,7 +7772,7 @@
       <c r="O31" s="8"/>
       <c r="P31" s="7"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:16">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -7751,7 +7790,7 @@
       <c r="O32" s="8"/>
       <c r="P32" s="7"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7769,7 +7808,7 @@
       <c r="O33" s="8"/>
       <c r="P33" s="7"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>

--- a/要件定義書.xlsx
+++ b/要件定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07931CFB-2907-4FE0-9FE0-14D927A37135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D04BAF-2326-4724-BA72-5559B27174E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="129">
   <si>
     <t>要件定義</t>
   </si>
@@ -291,33 +291,6 @@
   </si>
   <si>
     <t>3-2. 機能詳細</t>
-  </si>
-  <si>
-    <t>F-001 見積作成</t>
-  </si>
-  <si>
-    <t>・  顧客情報（顧客名・担当者・住所）の入力</t>
-  </si>
-  <si>
-    <t>・  商品の検索・追加、数量・単価の登録</t>
-  </si>
-  <si>
-    <t>・   自動計算機能（小計・税額・合計）</t>
-  </si>
-  <si>
-    <t>・  PDF 出力、メール送付機能</t>
-  </si>
-  <si>
-    <t>F-002 承認ワークフロー</t>
-  </si>
-  <si>
-    <t>・  申請→承認→確定の3ステップ</t>
-  </si>
-  <si>
-    <t>・   差戻し理由の記入を必須化</t>
-  </si>
-  <si>
-    <t>・   承認時メール通知を自動送信</t>
   </si>
   <si>
     <t>第5章</t>
@@ -523,42 +496,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>一般</t>
-    <rPh sb="0" eb="2">
-      <t>イッパン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>スケジュールカレンダー</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接日・担当者登録、面接希望者状況一覧閲覧</t>
-    <rPh sb="0" eb="3">
-      <t>メンセツビ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>メンセツキボウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>応募者登録</t>
     <rPh sb="0" eb="5">
       <t>オウボシャトウロク</t>
@@ -677,10 +614,6 @@
     <rPh sb="22" eb="24">
       <t>ハンエイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>全ユーザー</t>
     <phoneticPr fontId="13"/>
   </si>
   <si>
@@ -857,6 +790,67 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
+    <t>■応募者登録</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>選考状況の見える化</t>
+    <rPh sb="0" eb="4">
+      <t>センコウジョウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>面接未設定の人・選考状況をを一覧でわかりやすくし、全体で進捗把握の強化</t>
+    </r>
+    <rPh sb="1" eb="6">
+      <t>メンセツミセッテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="29" eb="33">
+      <t>シンチョクハアク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
     <r>
       <t>w</t>
     </r>
@@ -875,7 +869,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>問い合わせのあった応募者を一覧（面接設定日入り）で閲覧できるため</t>
+      <t>問い合わせのあった応募者を一覧（次回面接設定日・選考状況）で閲覧できるため</t>
     </r>
     <rPh sb="2" eb="3">
       <t>ト</t>
@@ -890,48 +884,255 @@
       <t>イチラン</t>
     </rPh>
     <rPh sb="18" eb="20">
+      <t>ジカイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
       <t>メンセツ</t>
     </rPh>
-    <rPh sb="20" eb="23">
+    <rPh sb="22" eb="25">
       <t>セッテイビ</t>
     </rPh>
-    <rPh sb="23" eb="24">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
+    <rPh sb="26" eb="30">
+      <t>センコウジョウキョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
       <t>エツラン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <charset val="128"/>
-      </rPr>
-      <t>面接未設定の人を一覧でわかりやすくし、全体で進捗把握の強化</t>
-    </r>
+    <t>・応募情報（氏名・カナ・性別・生年月日・メールアドレス・電話番号・郵便番号・住所・最終学歴・希望勤務地）の入力</t>
+    <rPh sb="1" eb="3">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <rPh sb="28" eb="32">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジュウショ</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>サイシュウガクレキ</t>
+    </rPh>
+    <rPh sb="46" eb="51">
+      <t>キボウキンムチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・上記情報のDBへの登録</t>
+    <rPh sb="1" eb="5">
+      <t>ジョウキジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■応募者状況一覧</t>
     <rPh sb="1" eb="6">
-      <t>メンセツミセッテイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヒト</t>
+      <t>オウボシャジョウキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募者情報を一覧表示（応募者ID・氏名・カナ・性別・メールアドレス・電話番号・応募日・面接予定日・選考状況・更新日時・担当者・合否・更新ボタン）</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
     </rPh>
     <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>ヨテイビ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ゴウヒ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・電話番号・面接予定日・選考状況・担当者・合否）</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>ヨテイビ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ゴウヒ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・更新ボタンより変更・登録が可能</t>
+    <rPh sb="1" eb="3">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用関連部署全ユーザー</t>
+    <rPh sb="0" eb="2">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>カンレンブショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接日・担当者登録、面接希望者状況一覧閲覧、スケジュールカレンダー</t>
+    <rPh sb="0" eb="3">
+      <t>メンセツビ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>メンセツキボウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="20" eb="22">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="23" eb="27">
-      <t>シンチョクハアク</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>キョウカ</t>
+    <rPh sb="19" eb="21">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■応募者検索</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■スケジュールカレンダー</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・採用スケジュールカレンダーへ自動反映</t>
+    <rPh sb="1" eb="3">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ジドウハンエイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1058,7 +1259,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1075,12 +1276,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1420,7 +1615,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1643,21 +1838,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1679,9 +1859,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1689,12 +1866,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1828,6 +1999,42 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2237,44 +2444,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="96"/>
-      <c r="B6" s="98"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="99" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="95"/>
-      <c r="P6" s="96"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="88"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="96"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="99" t="s">
+      <c r="A7" s="88"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="95"/>
-      <c r="P7" s="96"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="88"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2336,16 +2543,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="91" t="s">
+      <c r="F11" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="92"/>
-      <c r="H11" s="93" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="85" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2358,16 +2565,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="91" t="s">
+      <c r="F12" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="92"/>
-      <c r="H12" s="97">
+      <c r="G12" s="84"/>
+      <c r="H12" s="89">
         <v>46265</v>
       </c>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2380,14 +2587,14 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="91" t="s">
+      <c r="F13" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="92"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2400,14 +2607,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="91" t="s">
+      <c r="F14" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="92"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -2572,52 +2779,52 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="114" t="s">
+      <c r="B1" s="104"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="116"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="108"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="121"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="113"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="81"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="118"/>
-      <c r="O2" s="119"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="111"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="121"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="113"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -2643,427 +2850,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="122" t="s">
+      <c r="C4" s="115"/>
+      <c r="D4" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="123"/>
-      <c r="F4" s="122" t="s">
+      <c r="E4" s="115"/>
+      <c r="F4" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="124"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="122" t="s">
+      <c r="G4" s="116"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="124"/>
-      <c r="K4" s="124"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="124"/>
-      <c r="N4" s="124"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="123"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="115"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="111"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="102"/>
+      <c r="K5" s="102"/>
+      <c r="L5" s="102"/>
+      <c r="M5" s="102"/>
+      <c r="N5" s="102"/>
+      <c r="O5" s="102"/>
+      <c r="P5" s="102"/>
+      <c r="Q5" s="102"/>
+      <c r="R5" s="103"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="104"/>
-      <c r="O6" s="104"/>
-      <c r="P6" s="104"/>
-      <c r="Q6" s="104"/>
-      <c r="R6" s="105"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="104"/>
-      <c r="O7" s="104"/>
-      <c r="P7" s="104"/>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="105"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="97"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="100"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="104"/>
-      <c r="Q8" s="104"/>
-      <c r="R8" s="105"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="97"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="100"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="104"/>
-      <c r="K9" s="104"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="104"/>
-      <c r="O9" s="104"/>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="105"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="97"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="104"/>
-      <c r="P10" s="104"/>
-      <c r="Q10" s="104"/>
-      <c r="R10" s="105"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="97"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-      <c r="L11" s="104"/>
-      <c r="M11" s="104"/>
-      <c r="N11" s="104"/>
-      <c r="O11" s="104"/>
-      <c r="P11" s="104"/>
-      <c r="Q11" s="104"/>
-      <c r="R11" s="105"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="96"/>
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="97"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="104"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="104"/>
-      <c r="P12" s="104"/>
-      <c r="Q12" s="104"/>
-      <c r="R12" s="105"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="97"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="100"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="104"/>
-      <c r="L13" s="104"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="104"/>
-      <c r="O13" s="104"/>
-      <c r="P13" s="104"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="105"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="97"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="100"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
-      <c r="M14" s="104"/>
-      <c r="N14" s="104"/>
-      <c r="O14" s="104"/>
-      <c r="P14" s="104"/>
-      <c r="Q14" s="104"/>
-      <c r="R14" s="105"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="97"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="100"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="104"/>
-      <c r="O15" s="104"/>
-      <c r="P15" s="104"/>
-      <c r="Q15" s="104"/>
-      <c r="R15" s="105"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="97"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="100"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="100"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="101"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="104"/>
-      <c r="O16" s="104"/>
-      <c r="P16" s="104"/>
-      <c r="Q16" s="104"/>
-      <c r="R16" s="105"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="97"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="101"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
-      <c r="M17" s="104"/>
-      <c r="N17" s="104"/>
-      <c r="O17" s="104"/>
-      <c r="P17" s="104"/>
-      <c r="Q17" s="104"/>
-      <c r="R17" s="105"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="97"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="100"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="104"/>
-      <c r="Q18" s="104"/>
-      <c r="R18" s="105"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="96"/>
+      <c r="Q18" s="96"/>
+      <c r="R18" s="97"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="100"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="104"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="104"/>
-      <c r="O19" s="104"/>
-      <c r="P19" s="104"/>
-      <c r="Q19" s="104"/>
-      <c r="R19" s="105"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="96"/>
+      <c r="R19" s="97"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="100"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="101"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="104"/>
-      <c r="Q20" s="104"/>
-      <c r="R20" s="105"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="94"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="97"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="100"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="104"/>
-      <c r="O21" s="104"/>
-      <c r="P21" s="104"/>
-      <c r="Q21" s="104"/>
-      <c r="R21" s="105"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="96"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="96"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="97"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="100"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="100"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="101"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="104"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="104"/>
-      <c r="N22" s="104"/>
-      <c r="O22" s="104"/>
-      <c r="P22" s="104"/>
-      <c r="Q22" s="104"/>
-      <c r="R22" s="105"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="94"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="96"/>
+      <c r="N22" s="96"/>
+      <c r="O22" s="96"/>
+      <c r="P22" s="96"/>
+      <c r="Q22" s="96"/>
+      <c r="R22" s="97"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3299,23 +3506,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="79" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -3326,19 +3533,19 @@
       <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3371,14 +3578,14 @@
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="127"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="119"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3386,14 +3593,14 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="125" t="s">
+      <c r="K4" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="127"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="119"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3931,28 +4138,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="129" t="s">
+      <c r="D1" s="79"/>
+      <c r="E1" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="88"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="82"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -3962,25 +4169,29 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="88"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="82"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28"/>
+      <c r="M2" s="26" t="s">
+        <v>97</v>
+      </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="30"/>
+      <c r="O2" s="128">
+        <v>46266</v>
+      </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -4020,44 +4231,44 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="130" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
+      <c r="B5" s="122" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="122"/>
+      <c r="N5" s="122"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
       <c r="O6" s="36"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -4112,7 +4323,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4166,113 +4377,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="128" t="s">
+      <c r="B13" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="128"/>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="120"/>
+      <c r="J13" s="120"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="128" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="128"/>
-      <c r="K14" s="128"/>
-      <c r="L14" s="128"/>
-      <c r="M14" s="128"/>
-      <c r="N14" s="128"/>
-      <c r="O14" s="128"/>
+      <c r="B14" s="120" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="120"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="128" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="128"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
-      <c r="I15" s="128"/>
-      <c r="J15" s="128"/>
-      <c r="K15" s="128"/>
-      <c r="L15" s="128"/>
-      <c r="M15" s="128"/>
-      <c r="N15" s="128"/>
-      <c r="O15" s="128"/>
+      <c r="B15" s="120" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="120"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="120"/>
+      <c r="H15" s="120"/>
+      <c r="I15" s="120"/>
+      <c r="J15" s="120"/>
+      <c r="K15" s="120"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="120"/>
+      <c r="N15" s="120"/>
+      <c r="O15" s="120"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
-      <c r="B16" s="128" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="128"/>
-      <c r="G16" s="128"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="128"/>
-      <c r="J16" s="128"/>
-      <c r="K16" s="128"/>
-      <c r="L16" s="128"/>
-      <c r="M16" s="128"/>
-      <c r="N16" s="128"/>
-      <c r="O16" s="128"/>
+      <c r="B16" s="120" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="128"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="128"/>
-      <c r="K17" s="128"/>
-      <c r="L17" s="128"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="128"/>
-      <c r="O17" s="128"/>
+      <c r="B17" s="120" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="120"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="120"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="128"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="128"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="128"/>
-      <c r="H18" s="128"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="128"/>
-      <c r="K18" s="128"/>
-      <c r="L18" s="128"/>
-      <c r="M18" s="128"/>
-      <c r="N18" s="128"/>
-      <c r="O18" s="128"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
@@ -4313,7 +4526,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4385,7 +4598,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4404,7 +4617,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4423,7 +4636,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4477,7 +4690,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4496,7 +4709,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4515,7 +4728,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4570,35 +4783,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B23C175-7738-42CA-A6BE-4E914D9B5EA0}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="129" t="s">
+      <c r="D1" s="79"/>
+      <c r="E1" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="88"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="82"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4608,25 +4821,29 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="88"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="82"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="28"/>
+      <c r="M2" s="26" t="s">
+        <v>97</v>
+      </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="30"/>
+      <c r="O2" s="137">
+        <v>46266</v>
+      </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -4683,10 +4900,10 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
-      <c r="B6" s="133" t="s">
+      <c r="B6" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="134"/>
+      <c r="C6" s="126"/>
       <c r="D6" s="50" t="s">
         <v>43</v>
       </c>
@@ -4704,12 +4921,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
-      <c r="B7" s="131" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="132"/>
+      <c r="B7" s="123" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="124"/>
       <c r="D7" s="54" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -4725,41 +4942,37 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="131" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
+      <c r="B8" s="123" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="124"/>
+      <c r="D8" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
       <c r="H8" s="52"/>
       <c r="I8" s="23"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
       <c r="O8" s="36"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
-      <c r="B9" s="131" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="132"/>
-      <c r="D9" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="57"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
@@ -4784,37 +4997,37 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="36"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
@@ -4903,37 +5116,37 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
@@ -4969,56 +5182,56 @@
       <c r="N21" s="44"/>
       <c r="O21" s="44"/>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-    </row>
-    <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
+    <row r="22" spans="1:15" ht="26.5">
+      <c r="A22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
@@ -5073,7 +5286,7 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
+      <c r="B28" s="47"/>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
@@ -5090,20 +5303,20 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
@@ -5173,27 +5386,9 @@
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
     </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:K1"/>
@@ -5209,23 +5404,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8D2F9E-DCA9-4610-96AE-118D7871E7D7}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="10" max="10" width="10.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="84"/>
+      <c r="D1" s="79"/>
       <c r="E1" s="72" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F1" s="72"/>
       <c r="G1" s="72"/>
@@ -5236,27 +5431,27 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="85">
+      <c r="N1" s="138">
         <v>46260</v>
       </c>
-      <c r="O1" s="86"/>
+      <c r="O1" s="138"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="88"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="82"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5264,8 +5459,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="89"/>
-      <c r="O2" s="90"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="139"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5346,12 +5541,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5359,7 +5554,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5369,12 +5564,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5382,7 +5577,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5392,12 +5587,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5405,7 +5600,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5415,22 +5610,22 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="69" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="55"/>
       <c r="H10" s="55"/>
       <c r="I10" s="55"/>
       <c r="J10" s="56"/>
-      <c r="K10" s="70" t="s">
-        <v>122</v>
-      </c>
-      <c r="L10" s="56"/>
+      <c r="K10" s="135" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" s="136"/>
       <c r="M10" s="31"/>
       <c r="N10" s="36"/>
       <c r="O10" s="7"/>
@@ -5454,248 +5649,239 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="7"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
-      <c r="B13" s="76" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
+      <c r="B13" s="130" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
       <c r="M13" s="43"/>
       <c r="N13" s="43"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
-      <c r="B14" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
+      <c r="B14" s="131" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
-      <c r="B15" s="77" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="76"/>
+      <c r="B15" s="131" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="36"/>
-      <c r="B16" s="77" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="36"/>
-      <c r="B17" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76"/>
+      <c r="B17" s="131" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="130"/>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
+      <c r="B18" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="130"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="130"/>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
-      <c r="B19" s="74" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="130"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="130"/>
+      <c r="M19" s="130"/>
+      <c r="N19" s="43"/>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
-      <c r="B20" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="43"/>
+      <c r="B20" s="131" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="130"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="130"/>
+      <c r="K20" s="130"/>
+      <c r="L20" s="130"/>
+      <c r="M20" s="130"/>
       <c r="N20" s="43"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="76"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="76"/>
-      <c r="H21" s="76"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
+    <row r="21" spans="1:15" ht="18" customHeight="1">
+      <c r="A21" s="45"/>
+      <c r="B21" s="132" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="134"/>
+      <c r="D21" s="134"/>
+      <c r="E21" s="134"/>
+      <c r="F21" s="134"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="134"/>
+      <c r="N21" s="45"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
+    <row r="22" spans="1:15" ht="18" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="131" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
+    <row r="23" spans="1:15">
+      <c r="A23" s="8"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="47"/>
       <c r="O23" s="7"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
+      <c r="B24" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
       <c r="O24" s="7"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
+      <c r="B25" s="58" t="s">
+        <v>128</v>
+      </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
       <c r="E25" s="47"/>
@@ -5729,7 +5915,7 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
+      <c r="B27" s="47"/>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
       <c r="E27" s="47"/>
@@ -5746,36 +5932,36 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
       <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
       <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15">
@@ -5829,42 +6015,9 @@
       <c r="N32" s="8"/>
       <c r="O32" s="7"/>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="7"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="K10:L10"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="N1:O1"/>
@@ -5883,23 +6036,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="129" t="s">
+      <c r="D1" s="79"/>
+      <c r="E1" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="88"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="82"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -5914,17 +6067,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="88"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="82"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6513,23 +6666,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="129" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="79"/>
+      <c r="E1" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="88"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="82"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6544,17 +6697,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="88"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="82"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7177,23 +7330,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="129" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="79"/>
+      <c r="E1" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="88"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="82"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -7201,21 +7354,21 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="85"/>
-      <c r="P1" s="135"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="127"/>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="88"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="82"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7223,8 +7376,8 @@
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="91"/>
-      <c r="P2" s="92"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="84"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="41"/>

--- a/要件定義書.xlsx
+++ b/要件定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D04BAF-2326-4724-BA72-5559B27174E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD4EEC6-620F-49DB-8495-183123004015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="140">
   <si>
     <t>要件定義</t>
   </si>
@@ -215,37 +215,10 @@
     <t>備考</t>
   </si>
   <si>
-    <t>顧客名</t>
-  </si>
-  <si>
     <t>文字列</t>
   </si>
   <si>
     <t>必須</t>
-  </si>
-  <si>
-    <t>全角対応</t>
-  </si>
-  <si>
-    <t>電話番号</t>
-  </si>
-  <si>
-    <t>ハイフン許容</t>
-  </si>
-  <si>
-    <t>商品コード</t>
-  </si>
-  <si>
-    <t>マスタ参照</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>数値</t>
-  </si>
-  <si>
-    <t>1～99999</t>
   </si>
   <si>
     <t>リスク・課題</t>
@@ -1136,12 +1109,187 @@
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
+  <si>
+    <t>氏名</t>
+    <rPh sb="0" eb="2">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カナ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>性別</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>生年月日</t>
+    <rPh sb="0" eb="4">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>データ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>メールアドレス</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>電話番号</t>
+    <rPh sb="0" eb="4">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>郵便番号</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>住所</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>最終学歴</t>
+    <rPh sb="0" eb="4">
+      <t>サイシュウガクレキ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>希望勤務地</t>
+    <rPh sb="0" eb="5">
+      <t>キボウキンムチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>文字列</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>数値</t>
+    <rPh sb="0" eb="2">
+      <t>スウチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>全角</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ラジオボタン</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+年：1946～2026　月：1～12　日：1～31</t>
+    <rPh sb="6" eb="7">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ハイフンなし（ハイフンなしと表示する）</t>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+「中学校卒業」「高等学校卒業」「専門学校卒業」
+「短期大学卒業」「四年制大学卒業」「大学院修了」
+「その他」</t>
+    <rPh sb="7" eb="10">
+      <t>チュウガッコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="14" eb="20">
+      <t>コウトウガッコウソツギョウ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>センモンガッコウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>タンキダイガク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="39" eb="44">
+      <t>ヨネンセイダイガク</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="48" eb="53">
+      <t>ダイガクインシュウリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+「東京」「神奈川」「愛知」「大阪」「福岡」</t>
+    <rPh sb="7" eb="9">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カナガワ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>アイチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オオサカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フクオカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1257,6 +1405,13 @@
       <sz val="10"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1615,7 +1770,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1838,6 +1993,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1856,185 +2017,194 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2444,44 +2614,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="85"/>
+      <c r="B6" s="86"/>
       <c r="C6" s="87"/>
-      <c r="D6" s="91" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="90"/>
+      <c r="D6" s="88" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="86"/>
       <c r="O6" s="87"/>
-      <c r="P6" s="88"/>
+      <c r="P6" s="85"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="86"/>
       <c r="C7" s="87"/>
-      <c r="D7" s="91" t="s">
+      <c r="D7" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="90"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="86"/>
       <c r="O7" s="87"/>
-      <c r="P7" s="88"/>
+      <c r="P7" s="85"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2543,16 +2713,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="83" t="s">
+      <c r="F11" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="84"/>
-      <c r="H11" s="85" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="92"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2565,16 +2735,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="84"/>
-      <c r="H12" s="89">
+      <c r="G12" s="90"/>
+      <c r="H12" s="93">
         <v>46265</v>
       </c>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2587,14 +2757,14 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="84"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2607,14 +2777,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="83" t="s">
+      <c r="F14" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="84"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -2751,22 +2921,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2779,52 +2949,52 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="106" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="108"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="98"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="113"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="103"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="76"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="111"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="101"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="113"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="103"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -2850,427 +3020,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="115"/>
-      <c r="D4" s="114" t="s">
+      <c r="C4" s="105"/>
+      <c r="D4" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="115"/>
-      <c r="F4" s="114" t="s">
+      <c r="E4" s="105"/>
+      <c r="F4" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="116"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="114" t="s">
+      <c r="G4" s="106"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="115"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="105"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="102"/>
-      <c r="R5" s="103"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="111"/>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="111"/>
+      <c r="R5" s="112"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="96"/>
-      <c r="R6" s="97"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="117"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="118"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="95"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="96"/>
-      <c r="Q7" s="96"/>
-      <c r="R7" s="97"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
+      <c r="N7" s="117"/>
+      <c r="O7" s="117"/>
+      <c r="P7" s="117"/>
+      <c r="Q7" s="117"/>
+      <c r="R7" s="118"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="97"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="117"/>
+      <c r="O8" s="117"/>
+      <c r="P8" s="117"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="118"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="96"/>
-      <c r="O9" s="96"/>
-      <c r="P9" s="96"/>
-      <c r="Q9" s="96"/>
-      <c r="R9" s="97"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="118"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="97"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="114"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="117"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="118"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="97"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="117"/>
+      <c r="O11" s="117"/>
+      <c r="P11" s="117"/>
+      <c r="Q11" s="117"/>
+      <c r="R11" s="118"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="92"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="97"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="114"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="117"/>
+      <c r="O12" s="117"/>
+      <c r="P12" s="117"/>
+      <c r="Q12" s="117"/>
+      <c r="R12" s="118"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="92"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="97"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
+      <c r="O13" s="117"/>
+      <c r="P13" s="117"/>
+      <c r="Q13" s="117"/>
+      <c r="R13" s="118"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="92"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="97"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="117"/>
+      <c r="O14" s="117"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="117"/>
+      <c r="R14" s="118"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="92"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="97"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="118"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="92"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="92"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="97"/>
+      <c r="B16" s="113"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="117"/>
+      <c r="O16" s="117"/>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="117"/>
+      <c r="R16" s="118"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="97"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="117"/>
+      <c r="N17" s="117"/>
+      <c r="O17" s="117"/>
+      <c r="P17" s="117"/>
+      <c r="Q17" s="117"/>
+      <c r="R17" s="118"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
-      <c r="M18" s="96"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="97"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
+      <c r="N18" s="117"/>
+      <c r="O18" s="117"/>
+      <c r="P18" s="117"/>
+      <c r="Q18" s="117"/>
+      <c r="R18" s="118"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="92"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="96"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="96"/>
-      <c r="Q19" s="96"/>
-      <c r="R19" s="97"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="117"/>
+      <c r="N19" s="117"/>
+      <c r="O19" s="117"/>
+      <c r="P19" s="117"/>
+      <c r="Q19" s="117"/>
+      <c r="R19" s="118"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="92"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="96"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="97"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="116"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="117"/>
+      <c r="N20" s="117"/>
+      <c r="O20" s="117"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="117"/>
+      <c r="R20" s="118"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="92"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="96"/>
-      <c r="M21" s="96"/>
-      <c r="N21" s="96"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="96"/>
-      <c r="Q21" s="96"/>
-      <c r="R21" s="97"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="114"/>
+      <c r="I21" s="116"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="117"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="117"/>
+      <c r="R21" s="118"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="93"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-      <c r="K22" s="96"/>
-      <c r="L22" s="96"/>
-      <c r="M22" s="96"/>
-      <c r="N22" s="96"/>
-      <c r="O22" s="96"/>
-      <c r="P22" s="96"/>
-      <c r="Q22" s="96"/>
-      <c r="R22" s="97"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="117"/>
+      <c r="O22" s="117"/>
+      <c r="P22" s="117"/>
+      <c r="Q22" s="117"/>
+      <c r="R22" s="118"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3414,6 +3584,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:R22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:O2"/>
     <mergeCell ref="Q1:R1"/>
@@ -3422,78 +3664,6 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:R4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:R22"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3506,23 +3676,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="74" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -3533,19 +3703,19 @@
       <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3578,14 +3748,14 @@
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="119"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="121"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3593,14 +3763,14 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="117" t="s">
+      <c r="K4" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="119"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="121"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
@@ -4138,28 +4308,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="78" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="121" t="s">
+      <c r="D1" s="81"/>
+      <c r="E1" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="82"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4169,27 +4339,27 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="82"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="128">
+      <c r="O2" s="74">
         <v>46266</v>
       </c>
     </row>
@@ -4231,44 +4401,44 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="122" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="122"/>
+      <c r="B5" s="123" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="123"/>
+      <c r="I5" s="123"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="123"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
       <c r="O6" s="36"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -4323,7 +4493,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4377,115 +4547,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="120" t="s">
+      <c r="B13" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="120"/>
-      <c r="J13" s="120"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="122"/>
+      <c r="N13" s="122"/>
+      <c r="O13" s="122"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="120" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="120"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="120"/>
-      <c r="L14" s="120"/>
-      <c r="M14" s="120"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="120"/>
+      <c r="B14" s="122" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="122"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="122"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="120" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
+      <c r="B15" s="122" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="122"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="122"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
-      <c r="B16" s="120" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="120"/>
+      <c r="B16" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="122"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="122"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="122"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="120" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="120"/>
-      <c r="O17" s="120"/>
+      <c r="B17" s="122" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="122"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="122"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="120"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="120"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="K18" s="120"/>
-      <c r="L18" s="120"/>
-      <c r="M18" s="120"/>
-      <c r="N18" s="120"/>
-      <c r="O18" s="120"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="122"/>
+      <c r="O18" s="122"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
@@ -4526,7 +4696,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4598,7 +4768,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4617,7 +4787,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4636,7 +4806,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4690,7 +4860,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4709,7 +4879,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4728,7 +4898,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4790,28 +4960,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="78" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="121" t="s">
+      <c r="D1" s="81"/>
+      <c r="E1" s="82" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="82"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4821,27 +4991,27 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="82"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="137">
+      <c r="O2" s="75">
         <v>46266</v>
       </c>
     </row>
@@ -4900,10 +5070,10 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
-      <c r="B6" s="125" t="s">
+      <c r="B6" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="126"/>
+      <c r="C6" s="127"/>
       <c r="D6" s="50" t="s">
         <v>43</v>
       </c>
@@ -4921,12 +5091,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
-      <c r="B7" s="123" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="124"/>
+      <c r="B7" s="124" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="125"/>
       <c r="D7" s="54" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -4942,12 +5112,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="124"/>
+      <c r="C8" s="125"/>
       <c r="D8" s="17" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5411,16 +5581,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="78" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="79"/>
+      <c r="D1" s="81"/>
       <c r="E1" s="72" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F1" s="72"/>
       <c r="G1" s="72"/>
@@ -5431,27 +5601,27 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="138">
+      <c r="N1" s="130">
         <v>46260</v>
       </c>
-      <c r="O1" s="138"/>
+      <c r="O1" s="130"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="82"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="84"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5459,8 +5629,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="139"/>
-      <c r="O2" s="139"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5482,7 +5652,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5518,12 +5688,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
       <c r="B6" s="50" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="50" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
@@ -5531,7 +5701,7 @@
       <c r="I6" s="52"/>
       <c r="J6" s="67"/>
       <c r="K6" s="50" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L6" s="56"/>
       <c r="M6" s="71"/>
@@ -5541,12 +5711,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5554,7 +5724,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5564,12 +5734,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5577,7 +5747,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5587,12 +5757,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5600,7 +5770,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5610,22 +5780,22 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="69" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="55"/>
       <c r="H10" s="55"/>
       <c r="I10" s="55"/>
       <c r="J10" s="56"/>
-      <c r="K10" s="135" t="s">
-        <v>124</v>
-      </c>
-      <c r="L10" s="136"/>
+      <c r="K10" s="128" t="s">
+        <v>115</v>
+      </c>
+      <c r="L10" s="129"/>
       <c r="M10" s="31"/>
       <c r="N10" s="36"/>
       <c r="O10" s="7"/>
@@ -5649,183 +5819,183 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
-      <c r="B12" s="129" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
+      <c r="B12" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
-      <c r="B13" s="130" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
+      <c r="B13" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
       <c r="M13" s="43"/>
       <c r="N13" s="43"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
-      <c r="B14" s="131" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
+      <c r="B14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
-      <c r="B15" s="131" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
+      <c r="B15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="36"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="36"/>
-      <c r="B17" s="131" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
-      <c r="H17" s="132"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
+      <c r="B17" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="130"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="130"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="130"/>
+      <c r="B18" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
-      <c r="B19" s="133"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="130"/>
-      <c r="K19" s="130"/>
-      <c r="L19" s="130"/>
-      <c r="M19" s="130"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
       <c r="N19" s="43"/>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
-      <c r="B20" s="131" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="130"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="130"/>
-      <c r="K20" s="130"/>
-      <c r="L20" s="130"/>
-      <c r="M20" s="130"/>
+      <c r="B20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
       <c r="N20" s="43"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" ht="18" customHeight="1">
       <c r="A21" s="45"/>
-      <c r="B21" s="132" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="134"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="134"/>
+      <c r="B21" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
       <c r="N21" s="45"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
-      <c r="B22" s="131" t="s">
-        <v>123</v>
+      <c r="B22" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -5861,7 +6031,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="43" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
@@ -5880,7 +6050,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -6036,23 +6206,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="78" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="121" t="s">
+      <c r="D1" s="81"/>
+      <c r="E1" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="82"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6067,17 +6237,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="82"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6666,48 +6836,48 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="78" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="121" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="81"/>
+      <c r="E1" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="82"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="40">
-        <v>46001</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="82"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6781,11 +6951,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6793,11 +6963,11 @@
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6808,23 +6978,23 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" s="57"/>
       <c r="F7" s="54">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6835,23 +7005,23 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6859,132 +7029,188 @@
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9" s="57"/>
       <c r="H9" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I9" s="57"/>
-      <c r="J9" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="57"/>
+      <c r="J9" s="136" t="s">
+        <v>135</v>
+      </c>
+      <c r="K9" s="137"/>
+      <c r="L9" s="137"/>
+      <c r="M9" s="138"/>
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
+      <c r="B10" s="69" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="57"/>
+      <c r="F10" s="17">
+        <v>100</v>
+      </c>
+      <c r="G10" s="57"/>
+      <c r="H10" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="57"/>
       <c r="N10" s="8"/>
       <c r="O10" s="36"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="B11" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="57"/>
+      <c r="F11" s="17">
+        <v>11</v>
+      </c>
+      <c r="G11" s="57"/>
+      <c r="H11" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="57"/>
+      <c r="J11" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="57"/>
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
+      <c r="B12" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="57"/>
+      <c r="F12" s="17">
+        <v>7</v>
+      </c>
+      <c r="G12" s="57"/>
+      <c r="H12" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="57"/>
+      <c r="J12" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="57"/>
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
+      <c r="B13" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="134"/>
+      <c r="D13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="57"/>
+      <c r="F13" s="17">
+        <v>100</v>
+      </c>
+      <c r="G13" s="57"/>
+      <c r="H13" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="57"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="57"/>
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
+      <c r="B14" s="135" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="134"/>
+      <c r="D14" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="57"/>
+      <c r="F14" s="17">
+        <v>10</v>
+      </c>
+      <c r="G14" s="57"/>
+      <c r="H14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="57"/>
+      <c r="J14" s="140" t="s">
+        <v>137</v>
+      </c>
+      <c r="K14" s="141"/>
+      <c r="L14" s="141"/>
+      <c r="M14" s="142"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
+      <c r="B15" s="135" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="134"/>
+      <c r="D15" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" s="57"/>
+      <c r="F15" s="17">
+        <v>3</v>
+      </c>
+      <c r="G15" s="57"/>
+      <c r="H15" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="57"/>
+      <c r="J15" s="139" t="s">
+        <v>138</v>
+      </c>
+      <c r="K15" s="143"/>
+      <c r="L15" s="143"/>
+      <c r="M15" s="144"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
@@ -6998,10 +7224,10 @@
       <c r="G16" s="43"/>
       <c r="H16" s="43"/>
       <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="57"/>
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
@@ -7312,7 +7538,10 @@
       <c r="O34" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:K1"/>
@@ -7330,23 +7559,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="78" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="82"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="81"/>
+      <c r="E1" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -7354,21 +7583,21 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="80"/>
-      <c r="P1" s="127"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="133"/>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="82"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7376,8 +7605,8 @@
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="83"/>
-      <c r="P2" s="84"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="41"/>
@@ -7421,21 +7650,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="66"/>
       <c r="F5" s="52"/>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I5" s="66"/>
       <c r="J5" s="52"/>
       <c r="K5" s="52"/>
       <c r="L5" s="67"/>
       <c r="M5" s="61" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
@@ -7447,21 +7676,21 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="54" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
@@ -7473,21 +7702,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
       <c r="M7" s="54" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>

--- a/要件定義書.xlsx
+++ b/要件定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD4EEC6-620F-49DB-8495-183123004015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27D0025-1FBC-44FD-A954-C418E88E0D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="8" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="141">
   <si>
     <t>要件定義</t>
   </si>
@@ -231,24 +231,6 @@
   </si>
   <si>
     <t>対策</t>
-  </si>
-  <si>
-    <t>承認フローの遅延</t>
-  </si>
-  <si>
-    <t>業務遅延</t>
-  </si>
-  <si>
-    <t>通知機能で抑制</t>
-  </si>
-  <si>
-    <t>マスタ整備不足</t>
-  </si>
-  <si>
-    <t>誤入力発生</t>
-  </si>
-  <si>
-    <t>事前のマスタ登録強化</t>
   </si>
   <si>
     <t>3-1. 機能一覧</t>
@@ -1281,6 +1263,85 @@
     <t>渡辺のぞみ</t>
     <rPh sb="0" eb="2">
       <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>件数増えることでのスケジュール重複</t>
+    <rPh sb="0" eb="3">
+      <t>ケンスウフ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チョウフク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>要再度対応</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="1" eb="5">
+      <t>サイドタイオウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>メールにて担当者へ通知</t>
+    <rPh sb="5" eb="8">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一覧表示の際のデータ過多</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>表示に時間がかかる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ステータスの選択を作り、表示件数を絞る</t>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ヒョウジケンスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シボ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>非機能要件</t>
+    <rPh sb="0" eb="3">
+      <t>ヒキノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウケン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1770,7 +1831,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2167,12 +2228,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2205,6 +2260,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2618,7 +2676,7 @@
       <c r="B6" s="86"/>
       <c r="C6" s="87"/>
       <c r="D6" s="88" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E6" s="88"/>
       <c r="F6" s="88"/>
@@ -2718,7 +2776,7 @@
       </c>
       <c r="G11" s="90"/>
       <c r="H11" s="91" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="I11" s="92"/>
       <c r="J11" s="92"/>
@@ -4329,7 +4387,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4354,7 +4412,7 @@
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
@@ -4402,7 +4460,7 @@
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="123" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C5" s="123"/>
       <c r="D5" s="123"/>
@@ -4438,7 +4496,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -4493,7 +4551,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4567,7 +4625,7 @@
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="122" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C14" s="122"/>
       <c r="D14" s="122"/>
@@ -4586,7 +4644,7 @@
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="122" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C15" s="122"/>
       <c r="D15" s="122"/>
@@ -4605,7 +4663,7 @@
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
       <c r="B16" s="122" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C16" s="122"/>
       <c r="D16" s="122"/>
@@ -4624,7 +4682,7 @@
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
       <c r="B17" s="122" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C17" s="122"/>
       <c r="D17" s="122"/>
@@ -4696,7 +4754,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4768,7 +4826,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4787,7 +4845,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4806,7 +4864,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4860,7 +4918,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4879,7 +4937,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4898,7 +4956,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4981,7 +5039,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -5006,7 +5064,7 @@
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
@@ -5092,11 +5150,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="124" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C7" s="125"/>
       <c r="D7" s="54" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -5117,7 +5175,7 @@
       </c>
       <c r="C8" s="125"/>
       <c r="D8" s="17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5590,7 +5648,7 @@
       </c>
       <c r="D1" s="81"/>
       <c r="E1" s="72" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F1" s="72"/>
       <c r="G1" s="72"/>
@@ -5601,7 +5659,7 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
@@ -5652,7 +5710,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5688,12 +5746,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
       <c r="B6" s="50" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="50" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
@@ -5701,7 +5759,7 @@
       <c r="I6" s="52"/>
       <c r="J6" s="67"/>
       <c r="K6" s="50" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L6" s="56"/>
       <c r="M6" s="71"/>
@@ -5711,12 +5769,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5724,7 +5782,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5734,12 +5792,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5747,7 +5805,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5757,12 +5815,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5770,7 +5828,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5780,12 +5838,12 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="69" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="55"/>
@@ -5793,7 +5851,7 @@
       <c r="I10" s="55"/>
       <c r="J10" s="56"/>
       <c r="K10" s="128" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L10" s="129"/>
       <c r="M10" s="31"/>
@@ -5820,7 +5878,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="36" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -5828,7 +5886,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="43" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -5847,7 +5905,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C14" s="58"/>
       <c r="D14" s="58"/>
@@ -5866,7 +5924,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="58"/>
@@ -5902,7 +5960,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C17" s="58"/>
       <c r="D17" s="58"/>
@@ -5921,7 +5979,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="58" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
@@ -5957,7 +6015,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -5976,7 +6034,7 @@
     <row r="21" spans="1:15" ht="18" customHeight="1">
       <c r="A21" s="45"/>
       <c r="B21" s="58" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C21" s="45"/>
       <c r="D21" s="45"/>
@@ -5995,7 +6053,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -6031,7 +6089,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="43" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
@@ -6050,7 +6108,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -6841,7 +6899,7 @@
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="80" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D1" s="81"/>
       <c r="E1" s="82" t="s">
@@ -6857,7 +6915,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6951,11 +7009,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6967,7 +7025,7 @@
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6978,7 +7036,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
@@ -6994,7 +7052,7 @@
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -7005,11 +7063,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -7021,7 +7079,7 @@
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -7032,11 +7090,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -7047,23 +7105,23 @@
         <v>61</v>
       </c>
       <c r="I9" s="57"/>
-      <c r="J9" s="136" t="s">
-        <v>135</v>
-      </c>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="138"/>
+      <c r="J9" s="134" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
+      <c r="M9" s="136"/>
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="69" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E10" s="57"/>
       <c r="F10" s="17">
@@ -7084,11 +7142,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="17" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C11" s="57"/>
       <c r="D11" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="17">
@@ -7100,7 +7158,7 @@
       </c>
       <c r="I11" s="57"/>
       <c r="J11" s="17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -7111,11 +7169,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="17" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="17" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="17">
@@ -7127,7 +7185,7 @@
       </c>
       <c r="I12" s="57"/>
       <c r="J12" s="17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7138,11 +7196,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="134"/>
+        <v>122</v>
+      </c>
+      <c r="C13" s="132"/>
       <c r="D13" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="17">
@@ -7162,12 +7220,12 @@
     </row>
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="135" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="134"/>
+      <c r="B14" s="133" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="132"/>
       <c r="D14" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="17">
@@ -7178,23 +7236,23 @@
         <v>61</v>
       </c>
       <c r="I14" s="57"/>
-      <c r="J14" s="140" t="s">
-        <v>137</v>
-      </c>
-      <c r="K14" s="141"/>
-      <c r="L14" s="141"/>
-      <c r="M14" s="142"/>
+      <c r="J14" s="138" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="140"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="135" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="134"/>
+      <c r="B15" s="133" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="132"/>
       <c r="D15" s="17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E15" s="57"/>
       <c r="F15" s="17">
@@ -7205,12 +7263,12 @@
         <v>61</v>
       </c>
       <c r="I15" s="57"/>
-      <c r="J15" s="139" t="s">
-        <v>138</v>
-      </c>
-      <c r="K15" s="143"/>
-      <c r="L15" s="143"/>
-      <c r="M15" s="144"/>
+      <c r="J15" s="137" t="s">
+        <v>132</v>
+      </c>
+      <c r="K15" s="141"/>
+      <c r="L15" s="141"/>
+      <c r="M15" s="142"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
@@ -7564,7 +7622,7 @@
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="80" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D1" s="81"/>
       <c r="E1" s="82" t="s">
@@ -7579,12 +7637,15 @@
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="26"/>
+      <c r="M1" s="26" t="s">
+        <v>133</v>
+      </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="132"/>
-      <c r="P1" s="133"/>
+      <c r="O1" s="40">
+        <v>46268</v>
+      </c>
     </row>
     <row r="2" spans="1:16" ht="20">
       <c r="A2" s="78"/>
@@ -7605,8 +7666,7 @@
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="89"/>
-      <c r="P2" s="90"/>
+      <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="41"/>
@@ -7624,7 +7684,6 @@
       <c r="M3" s="41"/>
       <c r="N3" s="41"/>
       <c r="O3" s="36"/>
-      <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="8"/>
@@ -7642,7 +7701,6 @@
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
-      <c r="P4" s="7"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="8"/>
@@ -7668,7 +7726,6 @@
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
-      <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="36"/>
@@ -7676,25 +7733,27 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
-      <c r="M6" s="54" t="s">
-        <v>68</v>
+      <c r="M6" s="17" t="s">
+        <v>136</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
-      <c r="P6" s="7"/>
+      <c r="P6" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="36"/>
@@ -7702,25 +7761,24 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
-      <c r="M7" s="54" t="s">
-        <v>71</v>
+      <c r="M7" s="143" t="s">
+        <v>139</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>
-      <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="36"/>
@@ -7738,7 +7796,6 @@
       <c r="M8" s="54"/>
       <c r="N8" s="55"/>
       <c r="O8" s="56"/>
-      <c r="P8" s="7"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="36"/>
@@ -7756,7 +7813,6 @@
       <c r="M9" s="17"/>
       <c r="N9" s="23"/>
       <c r="O9" s="56"/>
-      <c r="P9" s="7"/>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="36"/>
@@ -7774,7 +7830,6 @@
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="36"/>
-      <c r="P10" s="7"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="36"/>
@@ -7792,7 +7847,6 @@
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
-      <c r="P11" s="7"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="36"/>
@@ -7810,7 +7864,6 @@
       <c r="M12" s="36"/>
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
-      <c r="P12" s="7"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="36"/>
@@ -7828,7 +7881,6 @@
       <c r="M13" s="43"/>
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
-      <c r="P13" s="7"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="36"/>
@@ -7846,7 +7898,6 @@
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
-      <c r="P14" s="7"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="36"/>
@@ -7864,7 +7915,6 @@
       <c r="M15" s="43"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
-      <c r="P15" s="7"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="36"/>
@@ -7882,9 +7932,8 @@
       <c r="M16" s="43"/>
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
-      <c r="P16" s="7"/>
-    </row>
-    <row r="17" spans="1:16">
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
@@ -7900,9 +7949,8 @@
       <c r="M17" s="43"/>
       <c r="N17" s="43"/>
       <c r="O17" s="43"/>
-      <c r="P17" s="7"/>
-    </row>
-    <row r="18" spans="1:16">
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
@@ -7918,9 +7966,8 @@
       <c r="M18" s="43"/>
       <c r="N18" s="43"/>
       <c r="O18" s="43"/>
-      <c r="P18" s="7"/>
-    </row>
-    <row r="19" spans="1:16">
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
@@ -7936,9 +7983,8 @@
       <c r="M19" s="60"/>
       <c r="N19" s="60"/>
       <c r="O19" s="60"/>
-      <c r="P19" s="7"/>
-    </row>
-    <row r="20" spans="1:16">
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
@@ -7954,9 +8000,8 @@
       <c r="M20" s="43"/>
       <c r="N20" s="43"/>
       <c r="O20" s="43"/>
-      <c r="P20" s="7"/>
-    </row>
-    <row r="21" spans="1:16">
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
@@ -7972,9 +8017,8 @@
       <c r="M21" s="43"/>
       <c r="N21" s="43"/>
       <c r="O21" s="43"/>
-      <c r="P21" s="7"/>
-    </row>
-    <row r="22" spans="1:16">
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="36"/>
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
@@ -7990,9 +8034,8 @@
       <c r="M22" s="43"/>
       <c r="N22" s="43"/>
       <c r="O22" s="43"/>
-      <c r="P22" s="7"/>
-    </row>
-    <row r="23" spans="1:16" ht="26.5">
+    </row>
+    <row r="23" spans="1:15" ht="26.5">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -8008,9 +8051,8 @@
       <c r="M23" s="45"/>
       <c r="N23" s="45"/>
       <c r="O23" s="45"/>
-      <c r="P23" s="7"/>
-    </row>
-    <row r="24" spans="1:16">
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -8026,9 +8068,8 @@
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
-      <c r="P24" s="7"/>
-    </row>
-    <row r="25" spans="1:16">
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58"/>
       <c r="C25" s="58"/>
@@ -8044,9 +8085,8 @@
       <c r="M25" s="58"/>
       <c r="N25" s="58"/>
       <c r="O25" s="58"/>
-      <c r="P25" s="7"/>
-    </row>
-    <row r="26" spans="1:16">
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="58"/>
       <c r="C26" s="58"/>
@@ -8062,9 +8102,8 @@
       <c r="M26" s="58"/>
       <c r="N26" s="58"/>
       <c r="O26" s="58"/>
-      <c r="P26" s="7"/>
-    </row>
-    <row r="27" spans="1:16">
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58"/>
       <c r="C27" s="58"/>
@@ -8080,9 +8119,8 @@
       <c r="M27" s="58"/>
       <c r="N27" s="58"/>
       <c r="O27" s="58"/>
-      <c r="P27" s="7"/>
-    </row>
-    <row r="28" spans="1:16">
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
@@ -8098,9 +8136,8 @@
       <c r="M28" s="58"/>
       <c r="N28" s="58"/>
       <c r="O28" s="58"/>
-      <c r="P28" s="7"/>
-    </row>
-    <row r="29" spans="1:16">
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
@@ -8116,9 +8153,8 @@
       <c r="M29" s="58"/>
       <c r="N29" s="58"/>
       <c r="O29" s="58"/>
-      <c r="P29" s="7"/>
-    </row>
-    <row r="30" spans="1:16">
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -8134,9 +8170,8 @@
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
-      <c r="P30" s="7"/>
-    </row>
-    <row r="31" spans="1:16">
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -8152,9 +8187,8 @@
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
       <c r="O31" s="8"/>
-      <c r="P31" s="7"/>
-    </row>
-    <row r="32" spans="1:16">
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -8170,9 +8204,8 @@
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
-      <c r="P32" s="7"/>
-    </row>
-    <row r="33" spans="1:16">
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -8188,9 +8221,8 @@
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
-      <c r="P33" s="7"/>
-    </row>
-    <row r="34" spans="1:16">
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -8206,17 +8238,14 @@
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
-      <c r="P34" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="5">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:K1"/>
-    <mergeCell ref="O1:P1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:K2"/>
-    <mergeCell ref="O2:P2"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
